--- a/Lab 02/graph/task3.xlsx
+++ b/Lab 02/graph/task3.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\chtay\Documents\FIT3143\FIT3143_lab01\Lab 02\graph\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6CE0DC49-C366-46BC-8ECC-DB8AFF7F115D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE3263DB-0F34-46D5-8489-633787F89E02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="20">
   <si>
     <t>N</t>
   </si>
@@ -58,6 +58,33 @@
   </si>
   <si>
     <t>Hybrid Cyclic (8 Processes x 16 Threads)</t>
+  </si>
+  <si>
+    <t>T/P</t>
+  </si>
+  <si>
+    <t>A Speedup</t>
+  </si>
+  <si>
+    <t>Open MPI Block Cyclic (# of processes increase)</t>
+  </si>
+  <si>
+    <t>Open MPI Cyclic (# of processes increase)</t>
+  </si>
+  <si>
+    <t>Hybrid Block-Cyclic (# of processes increase, # of threads = 2)</t>
+  </si>
+  <si>
+    <t>Hybrid Cyclic (# of processes increase, # of threads = 2)</t>
+  </si>
+  <si>
+    <t>Hybrid Block-Cyclic (# of processes = 2, # of threads increase)</t>
+  </si>
+  <si>
+    <t>Hybrid Cyclic (# of processes = 2, # of threads increase)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> E Speedup</t>
   </si>
 </sst>
 </file>
@@ -73,7 +100,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -83,6 +110,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.39997558519241921"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -159,7 +192,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -188,14 +221,45 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -476,14 +540,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:S34"/>
+  <dimension ref="A1:AF46"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="36" width="12.6328125" customWidth="1"/>
+    <col min="1" max="40" width="12.6328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" ht="30" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:23" ht="30" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="2" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -496,27 +560,31 @@
       </c>
       <c r="E2" s="10"/>
       <c r="F2" s="10"/>
-      <c r="G2" s="3"/>
-      <c r="H2" s="2" t="s">
+      <c r="G2" s="10"/>
+      <c r="H2" s="3"/>
+      <c r="I2" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="I2" s="10"/>
       <c r="J2" s="10"/>
       <c r="K2" s="10"/>
-      <c r="L2" s="2" t="s">
+      <c r="L2" s="10"/>
+      <c r="M2" s="10"/>
+      <c r="N2" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="M2" s="10"/>
-      <c r="N2" s="10"/>
-      <c r="O2" s="3"/>
-      <c r="P2" s="2" t="s">
+      <c r="O2" s="10"/>
+      <c r="P2" s="10"/>
+      <c r="Q2" s="10"/>
+      <c r="R2" s="3"/>
+      <c r="S2" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="Q2" s="10"/>
-      <c r="R2" s="10"/>
-      <c r="S2" s="10"/>
-    </row>
-    <row r="3" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="T2" s="10"/>
+      <c r="U2" s="10"/>
+      <c r="V2" s="10"/>
+      <c r="W2" s="10"/>
+    </row>
+    <row r="3" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A3" s="4"/>
       <c r="B3" s="5" t="s">
         <v>2</v>
@@ -536,44 +604,56 @@
       <c r="G3" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="H3" s="5" t="s">
+      <c r="H3" s="22" t="s">
+        <v>12</v>
+      </c>
+      <c r="I3" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="I3" s="11" t="s">
+      <c r="J3" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="J3" s="11" t="s">
+      <c r="K3" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="K3" s="14" t="s">
+      <c r="L3" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="M3" s="24" t="s">
+        <v>12</v>
+      </c>
+      <c r="N3" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="O3" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="P3" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q3" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="L3" s="5" t="s">
+      <c r="R3" s="22" t="s">
+        <v>12</v>
+      </c>
+      <c r="S3" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="M3" s="11" t="s">
+      <c r="T3" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="N3" s="11" t="s">
+      <c r="U3" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="O3" s="12" t="s">
+      <c r="V3" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="P3" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q3" s="11" t="s">
-        <v>5</v>
-      </c>
-      <c r="R3" s="11" t="s">
-        <v>3</v>
-      </c>
-      <c r="S3" s="14" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="W3" s="24" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A4" s="7">
         <v>10000000</v>
       </c>
@@ -584,11 +664,15 @@
         <v>1.833523</v>
       </c>
       <c r="G4" s="13"/>
-      <c r="K4" s="15"/>
-      <c r="O4" s="13"/>
-      <c r="S4" s="15"/>
-    </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="H4" s="23"/>
+      <c r="L4" s="13"/>
+      <c r="M4" s="25"/>
+      <c r="Q4" s="13"/>
+      <c r="R4" s="23"/>
+      <c r="V4" s="13"/>
+      <c r="W4" s="27"/>
+    </row>
+    <row r="5" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A5" s="7">
         <v>11000000</v>
       </c>
@@ -599,11 +683,15 @@
         <v>2.1030500000000001</v>
       </c>
       <c r="G5" s="13"/>
-      <c r="K5" s="15"/>
-      <c r="O5" s="13"/>
-      <c r="S5" s="15"/>
-    </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="H5" s="23"/>
+      <c r="L5" s="13"/>
+      <c r="M5" s="23"/>
+      <c r="Q5" s="13"/>
+      <c r="R5" s="23"/>
+      <c r="V5" s="13"/>
+      <c r="W5" s="27"/>
+    </row>
+    <row r="6" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A6" s="7">
         <v>12000000</v>
       </c>
@@ -614,11 +702,15 @@
         <v>2.3671989999999998</v>
       </c>
       <c r="G6" s="13"/>
-      <c r="K6" s="15"/>
-      <c r="O6" s="13"/>
-      <c r="S6" s="15"/>
-    </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="H6" s="23"/>
+      <c r="L6" s="13"/>
+      <c r="M6" s="23"/>
+      <c r="Q6" s="13"/>
+      <c r="R6" s="23"/>
+      <c r="V6" s="13"/>
+      <c r="W6" s="27"/>
+    </row>
+    <row r="7" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A7" s="7">
         <v>13000000</v>
       </c>
@@ -629,11 +721,16 @@
         <v>2.6392120000000001</v>
       </c>
       <c r="G7" s="13"/>
-      <c r="K7" s="15"/>
-      <c r="O7" s="13"/>
-      <c r="S7" s="15"/>
-    </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="H7" s="23"/>
+      <c r="L7" s="13"/>
+      <c r="M7" s="23"/>
+      <c r="Q7" s="13"/>
+      <c r="R7" s="26"/>
+      <c r="S7" s="16"/>
+      <c r="V7" s="13"/>
+      <c r="W7" s="27"/>
+    </row>
+    <row r="8" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A8" s="7">
         <v>14000000</v>
       </c>
@@ -644,11 +741,15 @@
         <v>2.9274079999999998</v>
       </c>
       <c r="G8" s="13"/>
-      <c r="K8" s="15"/>
-      <c r="O8" s="13"/>
-      <c r="S8" s="15"/>
-    </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="H8" s="23"/>
+      <c r="L8" s="13"/>
+      <c r="M8" s="23"/>
+      <c r="Q8" s="13"/>
+      <c r="R8" s="23"/>
+      <c r="V8" s="13"/>
+      <c r="W8" s="27"/>
+    </row>
+    <row r="9" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A9" s="7">
         <v>15000000</v>
       </c>
@@ -659,11 +760,15 @@
         <v>3.230092</v>
       </c>
       <c r="G9" s="13"/>
-      <c r="K9" s="15"/>
-      <c r="O9" s="13"/>
-      <c r="S9" s="15"/>
-    </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="H9" s="23"/>
+      <c r="L9" s="13"/>
+      <c r="M9" s="23"/>
+      <c r="Q9" s="13"/>
+      <c r="R9" s="23"/>
+      <c r="V9" s="13"/>
+      <c r="W9" s="27"/>
+    </row>
+    <row r="10" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A10" s="7">
         <v>16000000</v>
       </c>
@@ -674,11 +779,15 @@
         <v>3.5315159999999999</v>
       </c>
       <c r="G10" s="13"/>
-      <c r="K10" s="15"/>
-      <c r="O10" s="13"/>
-      <c r="S10" s="15"/>
-    </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="H10" s="23"/>
+      <c r="L10" s="13"/>
+      <c r="M10" s="23"/>
+      <c r="Q10" s="13"/>
+      <c r="R10" s="23"/>
+      <c r="V10" s="13"/>
+      <c r="W10" s="27"/>
+    </row>
+    <row r="11" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A11" s="7">
         <v>17000000</v>
       </c>
@@ -689,11 +798,15 @@
         <v>3.8283680000000002</v>
       </c>
       <c r="G11" s="13"/>
-      <c r="K11" s="15"/>
-      <c r="O11" s="13"/>
-      <c r="S11" s="15"/>
-    </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="H11" s="23"/>
+      <c r="L11" s="13"/>
+      <c r="M11" s="23"/>
+      <c r="Q11" s="13"/>
+      <c r="R11" s="23"/>
+      <c r="V11" s="13"/>
+      <c r="W11" s="27"/>
+    </row>
+    <row r="12" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A12" s="7">
         <v>18000000</v>
       </c>
@@ -704,11 +817,15 @@
         <v>4.154458</v>
       </c>
       <c r="G12" s="13"/>
-      <c r="K12" s="15"/>
-      <c r="O12" s="13"/>
-      <c r="S12" s="15"/>
-    </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="H12" s="23"/>
+      <c r="L12" s="13"/>
+      <c r="M12" s="23"/>
+      <c r="Q12" s="13"/>
+      <c r="R12" s="23"/>
+      <c r="V12" s="13"/>
+      <c r="W12" s="27"/>
+    </row>
+    <row r="13" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A13" s="7">
         <v>19000000</v>
       </c>
@@ -719,11 +836,15 @@
         <v>4.4743740000000001</v>
       </c>
       <c r="G13" s="13"/>
-      <c r="K13" s="15"/>
-      <c r="O13" s="13"/>
-      <c r="S13" s="15"/>
-    </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="H13" s="23"/>
+      <c r="L13" s="13"/>
+      <c r="M13" s="23"/>
+      <c r="Q13" s="13"/>
+      <c r="R13" s="23"/>
+      <c r="V13" s="13"/>
+      <c r="W13" s="27"/>
+    </row>
+    <row r="14" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A14" s="7">
         <v>20000000</v>
       </c>
@@ -734,11 +855,15 @@
         <v>4.8425269999999996</v>
       </c>
       <c r="G14" s="13"/>
-      <c r="K14" s="15"/>
-      <c r="O14" s="13"/>
-      <c r="S14" s="15"/>
-    </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="H14" s="23"/>
+      <c r="L14" s="13"/>
+      <c r="M14" s="23"/>
+      <c r="Q14" s="13"/>
+      <c r="R14" s="23"/>
+      <c r="V14" s="13"/>
+      <c r="W14" s="27"/>
+    </row>
+    <row r="15" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A15" s="7">
         <v>21000000</v>
       </c>
@@ -749,11 +874,15 @@
         <v>5.1548030000000002</v>
       </c>
       <c r="G15" s="13"/>
-      <c r="K15" s="15"/>
-      <c r="O15" s="13"/>
-      <c r="S15" s="15"/>
-    </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="H15" s="23"/>
+      <c r="L15" s="13"/>
+      <c r="M15" s="23"/>
+      <c r="Q15" s="13"/>
+      <c r="R15" s="23"/>
+      <c r="V15" s="13"/>
+      <c r="W15" s="27"/>
+    </row>
+    <row r="16" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A16" s="7">
         <v>22000000</v>
       </c>
@@ -764,11 +893,15 @@
         <v>5.5227000000000004</v>
       </c>
       <c r="G16" s="13"/>
-      <c r="K16" s="15"/>
-      <c r="O16" s="13"/>
-      <c r="S16" s="15"/>
-    </row>
-    <row r="17" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="H16" s="23"/>
+      <c r="L16" s="13"/>
+      <c r="M16" s="23"/>
+      <c r="Q16" s="13"/>
+      <c r="R16" s="23"/>
+      <c r="V16" s="13"/>
+      <c r="W16" s="27"/>
+    </row>
+    <row r="17" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A17" s="7">
         <v>23000000</v>
       </c>
@@ -779,11 +912,15 @@
         <v>5.8535399999999997</v>
       </c>
       <c r="G17" s="13"/>
-      <c r="K17" s="15"/>
-      <c r="O17" s="13"/>
-      <c r="S17" s="15"/>
-    </row>
-    <row r="18" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="H17" s="23"/>
+      <c r="L17" s="13"/>
+      <c r="M17" s="23"/>
+      <c r="Q17" s="13"/>
+      <c r="R17" s="23"/>
+      <c r="V17" s="13"/>
+      <c r="W17" s="27"/>
+    </row>
+    <row r="18" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A18" s="7">
         <v>24000000</v>
       </c>
@@ -794,11 +931,15 @@
         <v>6.2170909999999999</v>
       </c>
       <c r="G18" s="13"/>
-      <c r="K18" s="15"/>
-      <c r="O18" s="13"/>
-      <c r="S18" s="15"/>
-    </row>
-    <row r="19" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="H18" s="23"/>
+      <c r="L18" s="13"/>
+      <c r="M18" s="23"/>
+      <c r="Q18" s="13"/>
+      <c r="R18" s="23"/>
+      <c r="V18" s="13"/>
+      <c r="W18" s="27"/>
+    </row>
+    <row r="19" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A19" s="7">
         <v>25000000</v>
       </c>
@@ -809,11 +950,15 @@
         <v>6.5945340000000003</v>
       </c>
       <c r="G19" s="13"/>
-      <c r="K19" s="15"/>
-      <c r="O19" s="13"/>
-      <c r="S19" s="15"/>
-    </row>
-    <row r="20" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="H19" s="23"/>
+      <c r="L19" s="13"/>
+      <c r="M19" s="23"/>
+      <c r="Q19" s="13"/>
+      <c r="R19" s="23"/>
+      <c r="V19" s="13"/>
+      <c r="W19" s="27"/>
+    </row>
+    <row r="20" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A20" s="7">
         <v>26000000</v>
       </c>
@@ -824,11 +969,15 @@
         <v>6.9617089999999999</v>
       </c>
       <c r="G20" s="13"/>
-      <c r="K20" s="15"/>
-      <c r="O20" s="13"/>
-      <c r="S20" s="15"/>
-    </row>
-    <row r="21" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="H20" s="23"/>
+      <c r="L20" s="13"/>
+      <c r="M20" s="23"/>
+      <c r="Q20" s="13"/>
+      <c r="R20" s="23"/>
+      <c r="V20" s="13"/>
+      <c r="W20" s="27"/>
+    </row>
+    <row r="21" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A21" s="7">
         <v>27000000</v>
       </c>
@@ -839,11 +988,15 @@
         <v>7.322921</v>
       </c>
       <c r="G21" s="13"/>
-      <c r="K21" s="15"/>
-      <c r="O21" s="13"/>
-      <c r="S21" s="15"/>
-    </row>
-    <row r="22" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="H21" s="23"/>
+      <c r="L21" s="13"/>
+      <c r="M21" s="23"/>
+      <c r="Q21" s="13"/>
+      <c r="R21" s="23"/>
+      <c r="V21" s="13"/>
+      <c r="W21" s="27"/>
+    </row>
+    <row r="22" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A22" s="7">
         <v>28000000</v>
       </c>
@@ -854,11 +1007,15 @@
         <v>7.7059360000000003</v>
       </c>
       <c r="G22" s="13"/>
-      <c r="K22" s="15"/>
-      <c r="O22" s="13"/>
-      <c r="S22" s="15"/>
-    </row>
-    <row r="23" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="H22" s="23"/>
+      <c r="L22" s="13"/>
+      <c r="M22" s="23"/>
+      <c r="Q22" s="13"/>
+      <c r="R22" s="23"/>
+      <c r="V22" s="13"/>
+      <c r="W22" s="27"/>
+    </row>
+    <row r="23" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A23" s="7">
         <v>29000000</v>
       </c>
@@ -869,11 +1026,15 @@
         <v>8.0842749999999999</v>
       </c>
       <c r="G23" s="13"/>
-      <c r="K23" s="15"/>
-      <c r="O23" s="13"/>
-      <c r="S23" s="15"/>
-    </row>
-    <row r="24" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="H23" s="23"/>
+      <c r="L23" s="13"/>
+      <c r="M23" s="23"/>
+      <c r="Q23" s="13"/>
+      <c r="R23" s="23"/>
+      <c r="V23" s="13"/>
+      <c r="W23" s="27"/>
+    </row>
+    <row r="24" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A24" s="7">
         <v>30000000</v>
       </c>
@@ -884,11 +1045,15 @@
         <v>8.4775270000000003</v>
       </c>
       <c r="G24" s="13"/>
-      <c r="K24" s="15"/>
-      <c r="O24" s="13"/>
-      <c r="S24" s="15"/>
-    </row>
-    <row r="25" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="H24" s="23"/>
+      <c r="L24" s="13"/>
+      <c r="M24" s="23"/>
+      <c r="Q24" s="13"/>
+      <c r="R24" s="23"/>
+      <c r="V24" s="13"/>
+      <c r="W24" s="27"/>
+    </row>
+    <row r="25" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A25" s="7">
         <v>31000000</v>
       </c>
@@ -899,11 +1064,15 @@
         <v>8.9261719999999993</v>
       </c>
       <c r="G25" s="13"/>
-      <c r="K25" s="15"/>
-      <c r="O25" s="13"/>
-      <c r="S25" s="15"/>
-    </row>
-    <row r="26" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="H25" s="23"/>
+      <c r="L25" s="13"/>
+      <c r="M25" s="23"/>
+      <c r="Q25" s="13"/>
+      <c r="R25" s="23"/>
+      <c r="V25" s="13"/>
+      <c r="W25" s="27"/>
+    </row>
+    <row r="26" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A26" s="7">
         <v>32000000</v>
       </c>
@@ -914,11 +1083,15 @@
         <v>9.2956199999999995</v>
       </c>
       <c r="G26" s="13"/>
-      <c r="K26" s="15"/>
-      <c r="O26" s="13"/>
-      <c r="S26" s="15"/>
-    </row>
-    <row r="27" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="H26" s="23"/>
+      <c r="L26" s="13"/>
+      <c r="M26" s="23"/>
+      <c r="Q26" s="13"/>
+      <c r="R26" s="23"/>
+      <c r="V26" s="13"/>
+      <c r="W26" s="27"/>
+    </row>
+    <row r="27" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A27" s="7">
         <v>33000000</v>
       </c>
@@ -929,11 +1102,15 @@
         <v>9.7146369999999997</v>
       </c>
       <c r="G27" s="13"/>
-      <c r="K27" s="15"/>
-      <c r="O27" s="13"/>
-      <c r="S27" s="15"/>
-    </row>
-    <row r="28" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="H27" s="23"/>
+      <c r="L27" s="13"/>
+      <c r="M27" s="23"/>
+      <c r="Q27" s="13"/>
+      <c r="R27" s="23"/>
+      <c r="V27" s="13"/>
+      <c r="W27" s="27"/>
+    </row>
+    <row r="28" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A28" s="7">
         <v>34000000</v>
       </c>
@@ -944,11 +1121,15 @@
         <v>10.095466</v>
       </c>
       <c r="G28" s="13"/>
-      <c r="K28" s="15"/>
-      <c r="O28" s="13"/>
-      <c r="S28" s="15"/>
-    </row>
-    <row r="29" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="H28" s="23"/>
+      <c r="L28" s="13"/>
+      <c r="M28" s="23"/>
+      <c r="Q28" s="13"/>
+      <c r="R28" s="23"/>
+      <c r="V28" s="13"/>
+      <c r="W28" s="27"/>
+    </row>
+    <row r="29" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A29" s="7">
         <v>35000000</v>
       </c>
@@ -959,11 +1140,15 @@
         <v>10.571692000000001</v>
       </c>
       <c r="G29" s="13"/>
-      <c r="K29" s="15"/>
-      <c r="O29" s="13"/>
-      <c r="S29" s="15"/>
-    </row>
-    <row r="30" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="H29" s="23"/>
+      <c r="L29" s="13"/>
+      <c r="M29" s="23"/>
+      <c r="Q29" s="13"/>
+      <c r="R29" s="23"/>
+      <c r="V29" s="13"/>
+      <c r="W29" s="27"/>
+    </row>
+    <row r="30" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A30" s="7">
         <v>36000000</v>
       </c>
@@ -974,11 +1159,15 @@
         <v>11.142515</v>
       </c>
       <c r="G30" s="13"/>
-      <c r="K30" s="15"/>
-      <c r="O30" s="13"/>
-      <c r="S30" s="15"/>
-    </row>
-    <row r="31" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="H30" s="23"/>
+      <c r="L30" s="13"/>
+      <c r="M30" s="23"/>
+      <c r="Q30" s="13"/>
+      <c r="R30" s="23"/>
+      <c r="V30" s="13"/>
+      <c r="W30" s="27"/>
+    </row>
+    <row r="31" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A31" s="7">
         <v>37000000</v>
       </c>
@@ -989,11 +1178,15 @@
         <v>11.384838999999999</v>
       </c>
       <c r="G31" s="13"/>
-      <c r="K31" s="15"/>
-      <c r="O31" s="13"/>
-      <c r="S31" s="15"/>
-    </row>
-    <row r="32" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="H31" s="23"/>
+      <c r="L31" s="13"/>
+      <c r="M31" s="23"/>
+      <c r="Q31" s="13"/>
+      <c r="R31" s="23"/>
+      <c r="V31" s="13"/>
+      <c r="W31" s="27"/>
+    </row>
+    <row r="32" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A32" s="7">
         <v>38000000</v>
       </c>
@@ -1004,11 +1197,15 @@
         <v>11.813434000000001</v>
       </c>
       <c r="G32" s="13"/>
-      <c r="K32" s="15"/>
-      <c r="O32" s="13"/>
-      <c r="S32" s="15"/>
-    </row>
-    <row r="33" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="H32" s="23"/>
+      <c r="L32" s="13"/>
+      <c r="M32" s="23"/>
+      <c r="Q32" s="13"/>
+      <c r="R32" s="23"/>
+      <c r="V32" s="13"/>
+      <c r="W32" s="27"/>
+    </row>
+    <row r="33" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A33" s="7">
         <v>39000000</v>
       </c>
@@ -1019,11 +1216,15 @@
         <v>12.281571</v>
       </c>
       <c r="G33" s="13"/>
-      <c r="K33" s="15"/>
-      <c r="O33" s="13"/>
-      <c r="S33" s="15"/>
-    </row>
-    <row r="34" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="H33" s="23"/>
+      <c r="L33" s="13"/>
+      <c r="M33" s="23"/>
+      <c r="Q33" s="13"/>
+      <c r="R33" s="23"/>
+      <c r="V33" s="13"/>
+      <c r="W33" s="27"/>
+    </row>
+    <row r="34" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A34" s="7">
         <v>40000000</v>
       </c>
@@ -1034,18 +1235,486 @@
         <v>12.756418</v>
       </c>
       <c r="G34" s="13"/>
-      <c r="K34" s="15"/>
-      <c r="O34" s="13"/>
-      <c r="S34" s="15"/>
+      <c r="H34" s="23"/>
+      <c r="L34" s="13"/>
+      <c r="M34" s="23"/>
+      <c r="Q34" s="13"/>
+      <c r="R34" s="23"/>
+      <c r="V34" s="13"/>
+      <c r="W34" s="27"/>
+    </row>
+    <row r="35" spans="1:32" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="M35" s="14"/>
+    </row>
+    <row r="36" spans="1:32" x14ac:dyDescent="0.35">
+      <c r="A36" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B36" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="C36" s="19"/>
+      <c r="D36" s="19"/>
+      <c r="E36" s="19"/>
+      <c r="F36" s="1"/>
+      <c r="G36" s="18" t="s">
+        <v>14</v>
+      </c>
+      <c r="H36" s="19"/>
+      <c r="I36" s="19"/>
+      <c r="J36" s="19"/>
+      <c r="K36" s="1"/>
+      <c r="L36" s="18" t="s">
+        <v>15</v>
+      </c>
+      <c r="M36" s="19"/>
+      <c r="N36" s="19"/>
+      <c r="O36" s="19"/>
+      <c r="P36" s="1"/>
+      <c r="Q36" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="R36" s="19"/>
+      <c r="S36" s="19"/>
+      <c r="T36" s="19"/>
+      <c r="U36" s="1"/>
+      <c r="V36" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="W36" s="19"/>
+      <c r="X36" s="19"/>
+      <c r="Y36" s="19"/>
+      <c r="Z36" s="1"/>
+      <c r="AA36" s="18" t="s">
+        <v>18</v>
+      </c>
+      <c r="AB36" s="19"/>
+      <c r="AC36" s="19"/>
+      <c r="AD36" s="19"/>
+      <c r="AE36" s="19"/>
+      <c r="AF36" s="14"/>
+    </row>
+    <row r="37" spans="1:32" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A37" s="4"/>
+      <c r="B37" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="C37" s="21" t="s">
+        <v>5</v>
+      </c>
+      <c r="D37" s="21" t="s">
+        <v>3</v>
+      </c>
+      <c r="E37" s="30" t="s">
+        <v>6</v>
+      </c>
+      <c r="F37" s="28" t="s">
+        <v>12</v>
+      </c>
+      <c r="G37" s="21" t="s">
+        <v>4</v>
+      </c>
+      <c r="H37" s="21" t="s">
+        <v>5</v>
+      </c>
+      <c r="I37" s="21" t="s">
+        <v>3</v>
+      </c>
+      <c r="J37" s="30" t="s">
+        <v>6</v>
+      </c>
+      <c r="K37" s="28" t="s">
+        <v>12</v>
+      </c>
+      <c r="L37" s="21" t="s">
+        <v>4</v>
+      </c>
+      <c r="M37" s="21" t="s">
+        <v>5</v>
+      </c>
+      <c r="N37" s="21" t="s">
+        <v>3</v>
+      </c>
+      <c r="O37" s="30" t="s">
+        <v>6</v>
+      </c>
+      <c r="P37" s="28" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q37" s="21" t="s">
+        <v>4</v>
+      </c>
+      <c r="R37" s="21" t="s">
+        <v>5</v>
+      </c>
+      <c r="S37" s="21" t="s">
+        <v>3</v>
+      </c>
+      <c r="T37" s="30" t="s">
+        <v>6</v>
+      </c>
+      <c r="U37" s="28" t="s">
+        <v>12</v>
+      </c>
+      <c r="V37" s="21" t="s">
+        <v>4</v>
+      </c>
+      <c r="W37" s="21" t="s">
+        <v>5</v>
+      </c>
+      <c r="X37" s="21" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y37" s="30" t="s">
+        <v>6</v>
+      </c>
+      <c r="Z37" s="28" t="s">
+        <v>12</v>
+      </c>
+      <c r="AA37" s="21" t="s">
+        <v>4</v>
+      </c>
+      <c r="AB37" s="21" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC37" s="21" t="s">
+        <v>3</v>
+      </c>
+      <c r="AD37" s="30" t="s">
+        <v>6</v>
+      </c>
+      <c r="AE37" s="29" t="s">
+        <v>12</v>
+      </c>
+      <c r="AF37" s="14"/>
+    </row>
+    <row r="38" spans="1:32" x14ac:dyDescent="0.35">
+      <c r="A38" s="17">
+        <v>1</v>
+      </c>
+      <c r="B38" s="16"/>
+      <c r="C38" s="14"/>
+      <c r="D38" s="14"/>
+      <c r="E38" s="15"/>
+      <c r="F38" s="23"/>
+      <c r="G38" s="14"/>
+      <c r="H38" s="14"/>
+      <c r="I38" s="14"/>
+      <c r="J38" s="15"/>
+      <c r="K38" s="23"/>
+      <c r="L38" s="14"/>
+      <c r="M38" s="14"/>
+      <c r="N38" s="14"/>
+      <c r="O38" s="15"/>
+      <c r="P38" s="23"/>
+      <c r="Q38" s="14"/>
+      <c r="R38" s="14"/>
+      <c r="S38" s="14"/>
+      <c r="T38" s="15"/>
+      <c r="U38" s="23"/>
+      <c r="V38" s="14"/>
+      <c r="W38" s="14"/>
+      <c r="X38" s="14"/>
+      <c r="Y38" s="15"/>
+      <c r="Z38" s="23"/>
+      <c r="AA38" s="14"/>
+      <c r="AB38" s="14"/>
+      <c r="AC38" s="14"/>
+      <c r="AD38" s="15"/>
+      <c r="AE38" s="26"/>
+      <c r="AF38" s="14"/>
+    </row>
+    <row r="39" spans="1:32" x14ac:dyDescent="0.35">
+      <c r="A39" s="17">
+        <v>2</v>
+      </c>
+      <c r="B39" s="16"/>
+      <c r="C39" s="14"/>
+      <c r="D39" s="14"/>
+      <c r="E39" s="15"/>
+      <c r="F39" s="23"/>
+      <c r="G39" s="14"/>
+      <c r="H39" s="14"/>
+      <c r="I39" s="14"/>
+      <c r="J39" s="15"/>
+      <c r="K39" s="23"/>
+      <c r="L39" s="14"/>
+      <c r="M39" s="14"/>
+      <c r="N39" s="14"/>
+      <c r="O39" s="15"/>
+      <c r="P39" s="23"/>
+      <c r="Q39" s="14"/>
+      <c r="R39" s="14"/>
+      <c r="S39" s="14"/>
+      <c r="T39" s="15"/>
+      <c r="U39" s="23"/>
+      <c r="V39" s="14"/>
+      <c r="W39" s="14"/>
+      <c r="X39" s="14"/>
+      <c r="Y39" s="15"/>
+      <c r="Z39" s="23"/>
+      <c r="AA39" s="14"/>
+      <c r="AB39" s="14"/>
+      <c r="AC39" s="14"/>
+      <c r="AD39" s="15"/>
+      <c r="AE39" s="26"/>
+      <c r="AF39" s="14"/>
+    </row>
+    <row r="40" spans="1:32" x14ac:dyDescent="0.35">
+      <c r="A40" s="17">
+        <v>4</v>
+      </c>
+      <c r="B40" s="16"/>
+      <c r="C40" s="14"/>
+      <c r="D40" s="14"/>
+      <c r="E40" s="15"/>
+      <c r="F40" s="23"/>
+      <c r="G40" s="14"/>
+      <c r="H40" s="14"/>
+      <c r="I40" s="14"/>
+      <c r="J40" s="15"/>
+      <c r="K40" s="23"/>
+      <c r="L40" s="14"/>
+      <c r="M40" s="14"/>
+      <c r="N40" s="14"/>
+      <c r="O40" s="15"/>
+      <c r="P40" s="23"/>
+      <c r="Q40" s="14"/>
+      <c r="R40" s="14"/>
+      <c r="S40" s="14"/>
+      <c r="T40" s="15"/>
+      <c r="U40" s="23"/>
+      <c r="V40" s="14"/>
+      <c r="W40" s="14"/>
+      <c r="X40" s="14"/>
+      <c r="Y40" s="15"/>
+      <c r="Z40" s="23"/>
+      <c r="AA40" s="14"/>
+      <c r="AB40" s="14"/>
+      <c r="AC40" s="14"/>
+      <c r="AD40" s="15"/>
+      <c r="AE40" s="26"/>
+      <c r="AF40" s="14"/>
+    </row>
+    <row r="41" spans="1:32" x14ac:dyDescent="0.35">
+      <c r="A41" s="17">
+        <v>8</v>
+      </c>
+      <c r="B41" s="16"/>
+      <c r="C41" s="14"/>
+      <c r="D41" s="14"/>
+      <c r="E41" s="15"/>
+      <c r="F41" s="23"/>
+      <c r="G41" s="14"/>
+      <c r="H41" s="14"/>
+      <c r="I41" s="14"/>
+      <c r="J41" s="15"/>
+      <c r="K41" s="23"/>
+      <c r="L41" s="14"/>
+      <c r="M41" s="14"/>
+      <c r="N41" s="14"/>
+      <c r="O41" s="15"/>
+      <c r="P41" s="23"/>
+      <c r="Q41" s="14"/>
+      <c r="R41" s="14"/>
+      <c r="S41" s="14"/>
+      <c r="T41" s="15"/>
+      <c r="U41" s="23"/>
+      <c r="V41" s="14"/>
+      <c r="W41" s="14"/>
+      <c r="X41" s="14"/>
+      <c r="Y41" s="15"/>
+      <c r="Z41" s="23"/>
+      <c r="AA41" s="14"/>
+      <c r="AB41" s="14"/>
+      <c r="AC41" s="14"/>
+      <c r="AD41" s="15"/>
+      <c r="AE41" s="26"/>
+      <c r="AF41" s="14"/>
+    </row>
+    <row r="42" spans="1:32" x14ac:dyDescent="0.35">
+      <c r="A42" s="17">
+        <v>16</v>
+      </c>
+      <c r="B42" s="16"/>
+      <c r="C42" s="14"/>
+      <c r="D42" s="14"/>
+      <c r="E42" s="15"/>
+      <c r="F42" s="23"/>
+      <c r="G42" s="14"/>
+      <c r="H42" s="14"/>
+      <c r="I42" s="14"/>
+      <c r="J42" s="15"/>
+      <c r="K42" s="23"/>
+      <c r="L42" s="14"/>
+      <c r="M42" s="14"/>
+      <c r="N42" s="14"/>
+      <c r="O42" s="15"/>
+      <c r="P42" s="23"/>
+      <c r="Q42" s="14"/>
+      <c r="R42" s="14"/>
+      <c r="S42" s="14"/>
+      <c r="T42" s="15"/>
+      <c r="U42" s="23"/>
+      <c r="V42" s="14"/>
+      <c r="W42" s="14"/>
+      <c r="X42" s="14"/>
+      <c r="Y42" s="15"/>
+      <c r="Z42" s="23"/>
+      <c r="AA42" s="14"/>
+      <c r="AB42" s="14"/>
+      <c r="AC42" s="14"/>
+      <c r="AD42" s="15"/>
+      <c r="AE42" s="26"/>
+      <c r="AF42" s="14"/>
+    </row>
+    <row r="43" spans="1:32" x14ac:dyDescent="0.35">
+      <c r="A43" s="17">
+        <v>32</v>
+      </c>
+      <c r="B43" s="16"/>
+      <c r="C43" s="14"/>
+      <c r="D43" s="14"/>
+      <c r="E43" s="15"/>
+      <c r="F43" s="23"/>
+      <c r="G43" s="14"/>
+      <c r="H43" s="14"/>
+      <c r="I43" s="14"/>
+      <c r="J43" s="15"/>
+      <c r="K43" s="23"/>
+      <c r="L43" s="14"/>
+      <c r="M43" s="14"/>
+      <c r="N43" s="14"/>
+      <c r="O43" s="15"/>
+      <c r="P43" s="23"/>
+      <c r="Q43" s="14"/>
+      <c r="R43" s="14"/>
+      <c r="S43" s="14"/>
+      <c r="T43" s="15"/>
+      <c r="U43" s="23"/>
+      <c r="V43" s="14"/>
+      <c r="W43" s="14"/>
+      <c r="X43" s="14"/>
+      <c r="Y43" s="15"/>
+      <c r="Z43" s="23"/>
+      <c r="AA43" s="14"/>
+      <c r="AB43" s="14"/>
+      <c r="AC43" s="14"/>
+      <c r="AD43" s="15"/>
+      <c r="AE43" s="26"/>
+      <c r="AF43" s="14"/>
+    </row>
+    <row r="44" spans="1:32" x14ac:dyDescent="0.35">
+      <c r="A44" s="17">
+        <v>64</v>
+      </c>
+      <c r="B44" s="16"/>
+      <c r="C44" s="14"/>
+      <c r="D44" s="14"/>
+      <c r="E44" s="15"/>
+      <c r="F44" s="23"/>
+      <c r="G44" s="14"/>
+      <c r="H44" s="14"/>
+      <c r="I44" s="14"/>
+      <c r="J44" s="15"/>
+      <c r="K44" s="23"/>
+      <c r="L44" s="14"/>
+      <c r="M44" s="14"/>
+      <c r="N44" s="14"/>
+      <c r="O44" s="15"/>
+      <c r="P44" s="23"/>
+      <c r="Q44" s="14"/>
+      <c r="R44" s="14"/>
+      <c r="S44" s="14"/>
+      <c r="T44" s="15"/>
+      <c r="U44" s="23"/>
+      <c r="V44" s="14"/>
+      <c r="W44" s="14"/>
+      <c r="X44" s="14"/>
+      <c r="Y44" s="15"/>
+      <c r="Z44" s="23"/>
+      <c r="AA44" s="14"/>
+      <c r="AB44" s="14"/>
+      <c r="AC44" s="14"/>
+      <c r="AD44" s="15"/>
+      <c r="AE44" s="26"/>
+      <c r="AF44" s="14"/>
+    </row>
+    <row r="45" spans="1:32" x14ac:dyDescent="0.35">
+      <c r="A45" s="17">
+        <v>128</v>
+      </c>
+      <c r="B45" s="16"/>
+      <c r="C45" s="14"/>
+      <c r="D45" s="14"/>
+      <c r="E45" s="15"/>
+      <c r="F45" s="23"/>
+      <c r="G45" s="14"/>
+      <c r="H45" s="14"/>
+      <c r="I45" s="14"/>
+      <c r="J45" s="15"/>
+      <c r="K45" s="23"/>
+      <c r="L45" s="14"/>
+      <c r="M45" s="14"/>
+      <c r="N45" s="14"/>
+      <c r="O45" s="15"/>
+      <c r="P45" s="23"/>
+      <c r="Q45" s="14"/>
+      <c r="R45" s="14"/>
+      <c r="S45" s="14"/>
+      <c r="T45" s="15"/>
+      <c r="U45" s="23"/>
+      <c r="V45" s="14"/>
+      <c r="W45" s="14"/>
+      <c r="X45" s="14"/>
+      <c r="Y45" s="15"/>
+      <c r="Z45" s="23"/>
+      <c r="AA45" s="14"/>
+      <c r="AB45" s="14"/>
+      <c r="AC45" s="14"/>
+      <c r="AD45" s="15"/>
+      <c r="AE45" s="26"/>
+      <c r="AF45" s="14"/>
+    </row>
+    <row r="46" spans="1:32" x14ac:dyDescent="0.35">
+      <c r="K46" s="14"/>
+      <c r="L46" s="14"/>
+      <c r="M46" s="14"/>
+      <c r="N46" s="14"/>
+      <c r="O46" s="14"/>
+      <c r="P46" s="14"/>
+      <c r="Q46" s="14"/>
+      <c r="R46" s="14"/>
+      <c r="S46" s="14"/>
+      <c r="T46" s="14"/>
+      <c r="U46" s="14"/>
+      <c r="V46" s="14"/>
+      <c r="W46" s="14"/>
+      <c r="X46" s="14"/>
+      <c r="Y46" s="14"/>
+      <c r="Z46" s="14"/>
+      <c r="AA46" s="14"/>
+      <c r="AB46" s="14"/>
+      <c r="AC46" s="14"/>
+      <c r="AD46" s="14"/>
+      <c r="AE46" s="14"/>
+      <c r="AF46" s="14"/>
     </row>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells count="13">
+    <mergeCell ref="AA36:AE36"/>
+    <mergeCell ref="V36:Z36"/>
+    <mergeCell ref="Q36:U36"/>
+    <mergeCell ref="L36:P36"/>
+    <mergeCell ref="G36:K36"/>
+    <mergeCell ref="A36:A37"/>
+    <mergeCell ref="B36:F36"/>
     <mergeCell ref="A2:A3"/>
     <mergeCell ref="B2:C2"/>
-    <mergeCell ref="D2:G2"/>
-    <mergeCell ref="H2:K2"/>
-    <mergeCell ref="L2:O2"/>
-    <mergeCell ref="P2:S2"/>
+    <mergeCell ref="D2:H2"/>
+    <mergeCell ref="I2:M2"/>
+    <mergeCell ref="N2:R2"/>
+    <mergeCell ref="S2:W2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Lab 02/graph/task3.xlsx
+++ b/Lab 02/graph/task3.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\MONASH\Year_3_sem_1\FIT3143\Week 04\FIT3143_lab01\Lab 02\graph\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AEF27068-1F06-4708-921D-8173472A4AB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19504735-2A8F-4393-A1AB-89FEAE38B0BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="13776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="1" r:id="rId1"/>
@@ -108,8 +108,16 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -227,7 +235,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -300,6 +308,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -581,7 +595,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AH45"/>
+  <dimension ref="A1:AH57"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="43" width="12.6640625" customWidth="1"/>
@@ -3857,15 +3871,15 @@
       <c r="Q38">
         <v>1.0659155739999999</v>
       </c>
-      <c r="R38">
-        <v>2.8098820000000001E-3</v>
-      </c>
-      <c r="S38">
-        <v>1.1386344589999999</v>
+      <c r="R38" s="34">
+        <v>2.81E-3</v>
+      </c>
+      <c r="S38" s="34">
+        <v>1.1386339999999999</v>
       </c>
       <c r="T38" s="8">
         <f xml:space="preserve"> $C$4/S38</f>
-        <v>1.6102823742136545</v>
+        <v>1.6102830233420047</v>
       </c>
       <c r="U38" s="11">
         <f xml:space="preserve"> 1 / ((($S$38-$Q$38-$R$38)/$S$38) + (($Q$38/$S$38)/A38) + ($R$38/$S$38))</f>
@@ -3947,15 +3961,15 @@
       <c r="L39">
         <v>1.018369836</v>
       </c>
-      <c r="M39">
-        <v>2.6553950730000002</v>
+      <c r="M39" s="34">
+        <v>3.5184E-2</v>
       </c>
       <c r="N39">
-        <v>3.8089436000000001</v>
+        <v>1.1885485269999998</v>
       </c>
       <c r="O39" s="8">
         <f t="shared" ref="O39:O44" si="16">$C$4/N39</f>
-        <v>0.48137310303045705</v>
+        <v>1.5426572481882352</v>
       </c>
       <c r="P39" s="11">
         <f t="shared" ref="P39:P44" si="17" xml:space="preserve"> 1 / ((($N$38-$L$38-$M$38)/$N$38) + (($L$38/$N$38)/A39) + ($M$38/$N$38))</f>
@@ -3964,19 +3978,19 @@
       <c r="Q39">
         <v>1.041812325</v>
       </c>
-      <c r="R39">
-        <v>2.721912637</v>
-      </c>
-      <c r="S39">
-        <v>3.8667500220000002</v>
+      <c r="R39" s="34">
+        <v>4.0184699999999997E-2</v>
+      </c>
+      <c r="S39" s="34">
+        <v>1.1848369999999999</v>
       </c>
       <c r="T39" s="8">
         <f t="shared" ref="T39:T44" si="18" xml:space="preserve"> $C$4/S39</f>
-        <v>0.47417676073397846</v>
+        <v>1.5474896546951185</v>
       </c>
       <c r="U39" s="11">
         <f t="shared" ref="U39:U44" si="19" xml:space="preserve"> 1 / ((($S$38-$Q$38-$R$38)/$S$38) + (($Q$38/$S$38)/A39) + ($R$38/$S$38))</f>
-        <v>1.8799377813910589</v>
+        <v>1.8799384482348822</v>
       </c>
       <c r="V39">
         <v>0.12887994</v>
@@ -4054,15 +4068,15 @@
       <c r="L40">
         <v>1.0648632579999999</v>
       </c>
-      <c r="M40">
-        <v>8.7509943299999993</v>
+      <c r="M40" s="34">
+        <v>6.5326999999999996E-2</v>
       </c>
       <c r="N40">
-        <v>10.000580772999999</v>
+        <v>1.3145864399999998</v>
       </c>
       <c r="O40" s="8">
         <f t="shared" si="16"/>
-        <v>0.18334165201187363</v>
+        <v>1.3947527102135637</v>
       </c>
       <c r="P40" s="11">
         <f t="shared" si="17"/>
@@ -4071,19 +4085,19 @@
       <c r="Q40">
         <v>1.0409648359999999</v>
       </c>
-      <c r="R40">
-        <v>8.6902565440000004</v>
-      </c>
-      <c r="S40">
-        <v>9.9283791010000009</v>
+      <c r="R40" s="34">
+        <v>7.2326500000000002E-2</v>
+      </c>
+      <c r="S40" s="34">
+        <v>1.3101229999999999</v>
       </c>
       <c r="T40" s="8">
         <f t="shared" si="18"/>
-        <v>0.18467495865617428</v>
+        <v>1.3995044740074025</v>
       </c>
       <c r="U40" s="11">
         <f t="shared" si="19"/>
-        <v>3.3568452719097035</v>
+        <v>3.3568484611801299</v>
       </c>
       <c r="V40">
         <v>7.2493303999999995E-2</v>
@@ -4161,15 +4175,15 @@
       <c r="L41">
         <v>1.0649587389999999</v>
       </c>
-      <c r="M41">
-        <v>10.502509972</v>
+      <c r="M41" s="34">
+        <v>9.5641000000000004E-2</v>
       </c>
       <c r="N41">
-        <v>11.928449553</v>
+        <v>1.5209395799999996</v>
       </c>
       <c r="O41" s="8">
         <f t="shared" si="16"/>
-        <v>0.15371008544349082</v>
+        <v>1.2055199457693122</v>
       </c>
       <c r="P41" s="11">
         <f t="shared" si="17"/>
@@ -4178,19 +4192,19 @@
       <c r="Q41">
         <v>1.0649342040000001</v>
       </c>
-      <c r="R41">
-        <v>10.187021667</v>
-      </c>
-      <c r="S41">
-        <v>11.593793250999999</v>
+      <c r="R41" s="34">
+        <v>0.10541780000000001</v>
+      </c>
+      <c r="S41" s="34">
+        <v>1.5117719999999999</v>
       </c>
       <c r="T41" s="8">
         <f t="shared" si="18"/>
-        <v>0.15814694641392307</v>
+        <v>1.2128303738923596</v>
       </c>
       <c r="U41" s="11">
         <f t="shared" si="19"/>
-        <v>5.5284700032534611</v>
+        <v>5.5284800954519477</v>
       </c>
       <c r="V41">
         <v>6.0919776000000002E-2</v>
@@ -4268,15 +4282,15 @@
       <c r="L42">
         <v>0.54700426599999996</v>
       </c>
-      <c r="M42">
-        <v>10.292733159000001</v>
+      <c r="M42" s="34">
+        <v>0.145286</v>
       </c>
       <c r="N42">
-        <v>11.318997385999999</v>
+        <v>1.1712642300000007</v>
       </c>
       <c r="O42" s="8">
         <f t="shared" si="16"/>
-        <v>0.16198634361978109</v>
+        <v>1.5654221763435898</v>
       </c>
       <c r="P42" s="11">
         <f t="shared" si="17"/>
@@ -4285,19 +4299,19 @@
       <c r="Q42">
         <v>0.56189365800000002</v>
       </c>
-      <c r="R42">
-        <v>10.77451211</v>
-      </c>
-      <c r="S42">
-        <v>11.790303357000001</v>
+      <c r="R42" s="34">
+        <v>0.1582634</v>
+      </c>
+      <c r="S42" s="34">
+        <v>1.173791</v>
       </c>
       <c r="T42" s="8">
         <f t="shared" si="18"/>
-        <v>0.15551109623582521</v>
+        <v>1.5620523585544615</v>
       </c>
       <c r="U42" s="11">
         <f t="shared" si="19"/>
-        <v>8.1717082743901788</v>
+        <v>8.1717318990336274</v>
       </c>
       <c r="V42">
         <v>3.5633250999999998E-2</v>
@@ -4375,15 +4389,15 @@
       <c r="L43">
         <v>0.296927318</v>
       </c>
-      <c r="M43">
-        <v>10.670211469</v>
+      <c r="M43" s="34">
+        <v>0.22547300000000001</v>
       </c>
       <c r="N43">
-        <v>11.304260595000001</v>
+        <v>0.85904912999999927</v>
       </c>
       <c r="O43" s="8">
         <f t="shared" si="16"/>
-        <v>0.16219751699735122</v>
+        <v>2.1343633745371484</v>
       </c>
       <c r="P43" s="11">
         <f t="shared" si="17"/>
@@ -4392,19 +4406,19 @@
       <c r="Q43">
         <v>0.28799292999999998</v>
       </c>
-      <c r="R43">
-        <v>11.780282959000001</v>
-      </c>
-      <c r="S43">
-        <v>12.505373025000001</v>
+      <c r="R43" s="34">
+        <v>0.2456189</v>
+      </c>
+      <c r="S43" s="34">
+        <v>0.97009000000000001</v>
       </c>
       <c r="T43" s="8">
         <f t="shared" si="18"/>
-        <v>0.14661881707443108</v>
+        <v>1.8900545310228949</v>
       </c>
       <c r="U43" s="11">
         <f t="shared" si="19"/>
-        <v>10.738922175095713</v>
+        <v>10.738964335215206</v>
       </c>
       <c r="V43" s="17"/>
       <c r="W43" s="17"/>
@@ -4458,15 +4472,15 @@
       <c r="L44">
         <v>0.192948971</v>
       </c>
-      <c r="M44">
-        <v>11.062011138000001</v>
+      <c r="M44" s="34">
+        <v>0.33581899999999998</v>
       </c>
       <c r="N44">
-        <v>11.776869133</v>
+        <v>1.0498579900000005</v>
       </c>
       <c r="O44" s="8">
         <f t="shared" si="16"/>
-        <v>0.15568849235679114</v>
+        <v>1.7464485839651505</v>
       </c>
       <c r="P44" s="11">
         <f t="shared" si="17"/>
@@ -4475,19 +4489,19 @@
       <c r="Q44">
         <v>0.16893206599999999</v>
       </c>
-      <c r="R44">
-        <v>11.161608530000001</v>
-      </c>
-      <c r="S44">
-        <v>11.840179155</v>
+      <c r="R44" s="34">
+        <v>0.36527409999999999</v>
+      </c>
+      <c r="S44" s="34">
+        <v>1.043571</v>
       </c>
       <c r="T44" s="8">
         <f t="shared" si="18"/>
-        <v>0.15485601830828041</v>
+        <v>1.7569700576194625</v>
       </c>
       <c r="U44" s="11">
         <f t="shared" si="19"/>
-        <v>12.740134772701728</v>
+        <v>12.740195067201686</v>
       </c>
       <c r="V44" s="17"/>
       <c r="W44" s="17"/>
@@ -4559,6 +4573,47 @@
       <c r="AD45" s="17"/>
       <c r="AE45" s="17"/>
     </row>
+    <row r="49" spans="13:19" x14ac:dyDescent="0.3">
+      <c r="R49" s="33"/>
+      <c r="S49" s="33"/>
+    </row>
+    <row r="50" spans="13:19" x14ac:dyDescent="0.3">
+      <c r="R50" s="34"/>
+      <c r="S50" s="34"/>
+    </row>
+    <row r="51" spans="13:19" x14ac:dyDescent="0.3">
+      <c r="M51" s="33"/>
+      <c r="R51" s="34"/>
+      <c r="S51" s="34"/>
+    </row>
+    <row r="52" spans="13:19" x14ac:dyDescent="0.3">
+      <c r="M52" s="34"/>
+      <c r="R52" s="34"/>
+      <c r="S52" s="34"/>
+    </row>
+    <row r="53" spans="13:19" x14ac:dyDescent="0.3">
+      <c r="M53" s="34"/>
+      <c r="R53" s="34"/>
+      <c r="S53" s="34"/>
+    </row>
+    <row r="54" spans="13:19" x14ac:dyDescent="0.3">
+      <c r="M54" s="34"/>
+      <c r="R54" s="34"/>
+      <c r="S54" s="34"/>
+    </row>
+    <row r="55" spans="13:19" x14ac:dyDescent="0.3">
+      <c r="M55" s="34"/>
+      <c r="R55" s="34"/>
+      <c r="S55" s="34"/>
+    </row>
+    <row r="56" spans="13:19" x14ac:dyDescent="0.3">
+      <c r="M56" s="34"/>
+      <c r="R56" s="34"/>
+      <c r="S56" s="34"/>
+    </row>
+    <row r="57" spans="13:19" x14ac:dyDescent="0.3">
+      <c r="M57" s="34"/>
+    </row>
   </sheetData>
   <mergeCells count="13">
     <mergeCell ref="J2:O2"/>

--- a/Lab 02/graph/task3.xlsx
+++ b/Lab 02/graph/task3.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\MONASH\Year_3_sem_1\FIT3143\Week 04\FIT3143_lab01\Lab 02\graph\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\chtay\Documents\FIT3143\FIT3143_lab01\Lab 02\graph\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AEF27068-1F06-4708-921D-8173472A4AB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6C6EA18-E399-4ADB-9D76-6A8FFAB7ED8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="20" yWindow="20" windowWidth="19180" windowHeight="10060" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="1" r:id="rId1"/>
@@ -582,13 +582,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AH45"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="43" width="12.6640625" customWidth="1"/>
+    <col min="1" max="43" width="12.6328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" ht="30" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="2" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:27" ht="30" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="2" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A2" s="29" t="s">
         <v>0</v>
       </c>
@@ -629,7 +629,7 @@
       <c r="Z2" s="27"/>
       <c r="AA2" s="27"/>
     </row>
-    <row r="3" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A3" s="30"/>
       <c r="B3" s="2" t="s">
         <v>2</v>
@@ -710,7 +710,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="4" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A4" s="3">
         <v>10000000</v>
       </c>
@@ -805,7 +805,7 @@
         <v>23.155764620884476</v>
       </c>
     </row>
-    <row r="5" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A5" s="3">
         <v>11000000</v>
       </c>
@@ -900,7 +900,7 @@
         <v>24.678774876545287</v>
       </c>
     </row>
-    <row r="6" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A6" s="3">
         <v>12000000</v>
       </c>
@@ -995,7 +995,7 @@
         <v>26.364252250942798</v>
       </c>
     </row>
-    <row r="7" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A7" s="3">
         <v>13000000</v>
       </c>
@@ -1090,7 +1090,7 @@
         <v>24.77374814350906</v>
       </c>
     </row>
-    <row r="8" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A8" s="3">
         <v>14000000</v>
       </c>
@@ -1185,7 +1185,7 @@
         <v>23.05854157327871</v>
       </c>
     </row>
-    <row r="9" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A9" s="3">
         <v>15000000</v>
       </c>
@@ -1280,7 +1280,7 @@
         <v>19.111307092187349</v>
       </c>
     </row>
-    <row r="10" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A10" s="3">
         <v>16000000</v>
       </c>
@@ -1375,7 +1375,7 @@
         <v>24.489687872077951</v>
       </c>
     </row>
-    <row r="11" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A11" s="3">
         <v>17000000</v>
       </c>
@@ -1470,7 +1470,7 @@
         <v>23.295417230476378</v>
       </c>
     </row>
-    <row r="12" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A12" s="3">
         <v>18000000</v>
       </c>
@@ -1565,7 +1565,7 @@
         <v>25.011633793851875</v>
       </c>
     </row>
-    <row r="13" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A13" s="3">
         <v>19000000</v>
       </c>
@@ -1660,7 +1660,7 @@
         <v>26.7438257371814</v>
       </c>
     </row>
-    <row r="14" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A14" s="3">
         <v>20000000</v>
       </c>
@@ -1755,7 +1755,7 @@
         <v>10.563239452646634</v>
       </c>
     </row>
-    <row r="15" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A15" s="3">
         <v>21000000</v>
       </c>
@@ -1850,7 +1850,7 @@
         <v>23.882514296855348</v>
       </c>
     </row>
-    <row r="16" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A16" s="3">
         <v>22000000</v>
       </c>
@@ -1945,7 +1945,7 @@
         <v>27.660493917029822</v>
       </c>
     </row>
-    <row r="17" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A17" s="3">
         <v>23000000</v>
       </c>
@@ -2040,7 +2040,7 @@
         <v>26.092601184683282</v>
       </c>
     </row>
-    <row r="18" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A18" s="3">
         <v>24000000</v>
       </c>
@@ -2135,7 +2135,7 @@
         <v>27.104645041321181</v>
       </c>
     </row>
-    <row r="19" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A19" s="3">
         <v>25000000</v>
       </c>
@@ -2230,7 +2230,7 @@
         <v>29.057427144654277</v>
       </c>
     </row>
-    <row r="20" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A20" s="3">
         <v>26000000</v>
       </c>
@@ -2325,7 +2325,7 @@
         <v>17.577538641897902</v>
       </c>
     </row>
-    <row r="21" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A21" s="3">
         <v>27000000</v>
       </c>
@@ -2420,7 +2420,7 @@
         <v>28.418730901410331</v>
       </c>
     </row>
-    <row r="22" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A22" s="3">
         <v>28000000</v>
       </c>
@@ -2515,7 +2515,7 @@
         <v>26.49649266272646</v>
       </c>
     </row>
-    <row r="23" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A23" s="3">
         <v>29000000</v>
       </c>
@@ -2610,7 +2610,7 @@
         <v>25.43009782002019</v>
       </c>
     </row>
-    <row r="24" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A24" s="3">
         <v>30000000</v>
       </c>
@@ -2705,7 +2705,7 @@
         <v>26.656977129826263</v>
       </c>
     </row>
-    <row r="25" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A25" s="3">
         <v>31000000</v>
       </c>
@@ -2800,7 +2800,7 @@
         <v>25.754491580686082</v>
       </c>
     </row>
-    <row r="26" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A26" s="3">
         <v>32000000</v>
       </c>
@@ -2895,7 +2895,7 @@
         <v>26.902515152649535</v>
       </c>
     </row>
-    <row r="27" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A27" s="3">
         <v>33000000</v>
       </c>
@@ -2990,7 +2990,7 @@
         <v>18.274430179689041</v>
       </c>
     </row>
-    <row r="28" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A28" s="3">
         <v>34000000</v>
       </c>
@@ -3085,7 +3085,7 @@
         <v>26.538924435571356</v>
       </c>
     </row>
-    <row r="29" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A29" s="3">
         <v>35000000</v>
       </c>
@@ -3180,7 +3180,7 @@
         <v>27.977674769127194</v>
       </c>
     </row>
-    <row r="30" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A30" s="3">
         <v>36000000</v>
       </c>
@@ -3275,7 +3275,7 @@
         <v>16.686725714776461</v>
       </c>
     </row>
-    <row r="31" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A31" s="3">
         <v>37000000</v>
       </c>
@@ -3370,7 +3370,7 @@
         <v>18.235216985098198</v>
       </c>
     </row>
-    <row r="32" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A32" s="3">
         <v>38000000</v>
       </c>
@@ -3465,7 +3465,7 @@
         <v>23.595231235349701</v>
       </c>
     </row>
-    <row r="33" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A33" s="3">
         <v>39000000</v>
       </c>
@@ -3560,7 +3560,7 @@
         <v>31.268843299276909</v>
       </c>
     </row>
-    <row r="34" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A34" s="3">
         <v>40000000</v>
       </c>
@@ -3655,8 +3655,8 @@
         <v>30.267147393906434</v>
       </c>
     </row>
-    <row r="35" spans="1:34" ht="30" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="36" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:34" ht="30" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="36" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A36" s="29" t="s">
         <v>11</v>
       </c>
@@ -3706,7 +3706,7 @@
       <c r="AG36" s="19"/>
       <c r="AH36" s="19"/>
     </row>
-    <row r="37" spans="1:34" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:34" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A37" s="30"/>
       <c r="B37" s="9" t="s">
         <v>4</v>
@@ -3799,7 +3799,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="38" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A38" s="24">
         <v>1</v>
       </c>
@@ -3906,7 +3906,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A39" s="3">
         <v>2</v>
       </c>
@@ -4013,7 +4013,7 @@
         <v>1.4097352647191121</v>
       </c>
     </row>
-    <row r="40" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A40" s="3">
         <v>4</v>
       </c>
@@ -4120,7 +4120,7 @@
         <v>1.7729567077020183</v>
       </c>
     </row>
-    <row r="41" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A41" s="3">
         <v>8</v>
       </c>
@@ -4227,7 +4227,7 @@
         <v>2.0351352861161032</v>
       </c>
     </row>
-    <row r="42" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A42" s="3">
         <v>16</v>
       </c>
@@ -4334,7 +4334,7 @@
         <v>2.1976237033244055</v>
       </c>
     </row>
-    <row r="43" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A43" s="3">
         <v>32</v>
       </c>
@@ -4417,7 +4417,7 @@
       <c r="AD43" s="17"/>
       <c r="AE43" s="17"/>
     </row>
-    <row r="44" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A44" s="3">
         <v>64</v>
       </c>
@@ -4500,7 +4500,7 @@
       <c r="AD44" s="17"/>
       <c r="AE44" s="17"/>
     </row>
-    <row r="45" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A45" s="3">
         <v>128</v>
       </c>

--- a/Lab 02/graph/task3.xlsx
+++ b/Lab 02/graph/task3.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\chtay\Documents\FIT3143\FIT3143_lab01\Lab 02\graph\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6C6EA18-E399-4ADB-9D76-6A8FFAB7ED8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{7B9EF999-63DD-4DF1-B809-0247109D0445}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20" yWindow="20" windowWidth="19180" windowHeight="10060" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="1" r:id="rId1"/>
@@ -108,8 +108,16 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -227,7 +235,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -300,6 +308,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -581,14 +595,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AH45"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:AH58"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="43" width="12.6328125" customWidth="1"/>
+    <col min="1" max="43" width="12.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" ht="30" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="2" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:27" ht="30" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A2" s="29" t="s">
         <v>0</v>
       </c>
@@ -629,7 +643,7 @@
       <c r="Z2" s="27"/>
       <c r="AA2" s="27"/>
     </row>
-    <row r="3" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="30"/>
       <c r="B3" s="2" t="s">
         <v>2</v>
@@ -710,7 +724,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="4" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A4" s="3">
         <v>10000000</v>
       </c>
@@ -805,7 +819,7 @@
         <v>23.155764620884476</v>
       </c>
     </row>
-    <row r="5" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A5" s="3">
         <v>11000000</v>
       </c>
@@ -900,7 +914,7 @@
         <v>24.678774876545287</v>
       </c>
     </row>
-    <row r="6" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A6" s="3">
         <v>12000000</v>
       </c>
@@ -995,7 +1009,7 @@
         <v>26.364252250942798</v>
       </c>
     </row>
-    <row r="7" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A7" s="3">
         <v>13000000</v>
       </c>
@@ -1090,7 +1104,7 @@
         <v>24.77374814350906</v>
       </c>
     </row>
-    <row r="8" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A8" s="3">
         <v>14000000</v>
       </c>
@@ -1185,7 +1199,7 @@
         <v>23.05854157327871</v>
       </c>
     </row>
-    <row r="9" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A9" s="3">
         <v>15000000</v>
       </c>
@@ -1280,7 +1294,7 @@
         <v>19.111307092187349</v>
       </c>
     </row>
-    <row r="10" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A10" s="3">
         <v>16000000</v>
       </c>
@@ -1375,7 +1389,7 @@
         <v>24.489687872077951</v>
       </c>
     </row>
-    <row r="11" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A11" s="3">
         <v>17000000</v>
       </c>
@@ -1470,7 +1484,7 @@
         <v>23.295417230476378</v>
       </c>
     </row>
-    <row r="12" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A12" s="3">
         <v>18000000</v>
       </c>
@@ -1565,7 +1579,7 @@
         <v>25.011633793851875</v>
       </c>
     </row>
-    <row r="13" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A13" s="3">
         <v>19000000</v>
       </c>
@@ -1660,7 +1674,7 @@
         <v>26.7438257371814</v>
       </c>
     </row>
-    <row r="14" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A14" s="3">
         <v>20000000</v>
       </c>
@@ -1755,7 +1769,7 @@
         <v>10.563239452646634</v>
       </c>
     </row>
-    <row r="15" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A15" s="3">
         <v>21000000</v>
       </c>
@@ -1850,7 +1864,7 @@
         <v>23.882514296855348</v>
       </c>
     </row>
-    <row r="16" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A16" s="3">
         <v>22000000</v>
       </c>
@@ -1945,7 +1959,7 @@
         <v>27.660493917029822</v>
       </c>
     </row>
-    <row r="17" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A17" s="3">
         <v>23000000</v>
       </c>
@@ -2040,7 +2054,7 @@
         <v>26.092601184683282</v>
       </c>
     </row>
-    <row r="18" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A18" s="3">
         <v>24000000</v>
       </c>
@@ -2135,7 +2149,7 @@
         <v>27.104645041321181</v>
       </c>
     </row>
-    <row r="19" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A19" s="3">
         <v>25000000</v>
       </c>
@@ -2230,7 +2244,7 @@
         <v>29.057427144654277</v>
       </c>
     </row>
-    <row r="20" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A20" s="3">
         <v>26000000</v>
       </c>
@@ -2325,7 +2339,7 @@
         <v>17.577538641897902</v>
       </c>
     </row>
-    <row r="21" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A21" s="3">
         <v>27000000</v>
       </c>
@@ -2420,7 +2434,7 @@
         <v>28.418730901410331</v>
       </c>
     </row>
-    <row r="22" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A22" s="3">
         <v>28000000</v>
       </c>
@@ -2515,7 +2529,7 @@
         <v>26.49649266272646</v>
       </c>
     </row>
-    <row r="23" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A23" s="3">
         <v>29000000</v>
       </c>
@@ -2610,7 +2624,7 @@
         <v>25.43009782002019</v>
       </c>
     </row>
-    <row r="24" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A24" s="3">
         <v>30000000</v>
       </c>
@@ -2705,7 +2719,7 @@
         <v>26.656977129826263</v>
       </c>
     </row>
-    <row r="25" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A25" s="3">
         <v>31000000</v>
       </c>
@@ -2800,7 +2814,7 @@
         <v>25.754491580686082</v>
       </c>
     </row>
-    <row r="26" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A26" s="3">
         <v>32000000</v>
       </c>
@@ -2895,7 +2909,7 @@
         <v>26.902515152649535</v>
       </c>
     </row>
-    <row r="27" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A27" s="3">
         <v>33000000</v>
       </c>
@@ -2990,7 +3004,7 @@
         <v>18.274430179689041</v>
       </c>
     </row>
-    <row r="28" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A28" s="3">
         <v>34000000</v>
       </c>
@@ -3085,7 +3099,7 @@
         <v>26.538924435571356</v>
       </c>
     </row>
-    <row r="29" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A29" s="3">
         <v>35000000</v>
       </c>
@@ -3180,7 +3194,7 @@
         <v>27.977674769127194</v>
       </c>
     </row>
-    <row r="30" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A30" s="3">
         <v>36000000</v>
       </c>
@@ -3275,7 +3289,7 @@
         <v>16.686725714776461</v>
       </c>
     </row>
-    <row r="31" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A31" s="3">
         <v>37000000</v>
       </c>
@@ -3370,7 +3384,7 @@
         <v>18.235216985098198</v>
       </c>
     </row>
-    <row r="32" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A32" s="3">
         <v>38000000</v>
       </c>
@@ -3465,7 +3479,7 @@
         <v>23.595231235349701</v>
       </c>
     </row>
-    <row r="33" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A33" s="3">
         <v>39000000</v>
       </c>
@@ -3560,7 +3574,7 @@
         <v>31.268843299276909</v>
       </c>
     </row>
-    <row r="34" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A34" s="3">
         <v>40000000</v>
       </c>
@@ -3655,8 +3669,8 @@
         <v>30.267147393906434</v>
       </c>
     </row>
-    <row r="35" spans="1:34" ht="30" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="36" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:34" ht="30" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="36" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A36" s="29" t="s">
         <v>11</v>
       </c>
@@ -3706,7 +3720,7 @@
       <c r="AG36" s="19"/>
       <c r="AH36" s="19"/>
     </row>
-    <row r="37" spans="1:34" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:34" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A37" s="30"/>
       <c r="B37" s="9" t="s">
         <v>4</v>
@@ -3799,7 +3813,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="38" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A38" s="24">
         <v>1</v>
       </c>
@@ -3844,11 +3858,11 @@
         <v>2.6982260000000002E-3</v>
       </c>
       <c r="N38">
-        <v>1.0906670039999999</v>
+        <v>1.0906670000000001</v>
       </c>
       <c r="O38" s="8">
         <f>$C$4/N38</f>
-        <v>1.681102475160237</v>
+        <v>1.6811024813256474</v>
       </c>
       <c r="P38" s="11">
         <f xml:space="preserve"> 1 / ((($N$38-$L$38-$M$38)/$N$38) + (($L$38/$N$38)/A38) + ($M$38/$N$38))</f>
@@ -3858,14 +3872,14 @@
         <v>1.0659155739999999</v>
       </c>
       <c r="R38">
-        <v>2.8098820000000001E-3</v>
+        <v>2.81E-3</v>
       </c>
       <c r="S38">
-        <v>1.1386344589999999</v>
+        <v>1.1386339999999999</v>
       </c>
       <c r="T38" s="8">
         <f xml:space="preserve"> $C$4/S38</f>
-        <v>1.6102823742136545</v>
+        <v>1.6102830233420047</v>
       </c>
       <c r="U38" s="11">
         <f xml:space="preserve"> 1 / ((($S$38-$Q$38-$R$38)/$S$38) + (($Q$38/$S$38)/A38) + ($R$38/$S$38))</f>
@@ -3906,7 +3920,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A39" s="3">
         <v>2</v>
       </c>
@@ -3948,35 +3962,35 @@
         <v>1.018369836</v>
       </c>
       <c r="M39">
-        <v>2.6553950730000002</v>
+        <v>3.5184E-2</v>
       </c>
       <c r="N39">
-        <v>3.8089436000000001</v>
+        <v>1.1885490000000001</v>
       </c>
       <c r="O39" s="8">
         <f t="shared" ref="O39:O44" si="16">$C$4/N39</f>
-        <v>0.48137310303045705</v>
+        <v>1.5426566342658148</v>
       </c>
       <c r="P39" s="11">
         <f t="shared" ref="P39:P44" si="17" xml:space="preserve"> 1 / ((($N$38-$L$38-$M$38)/$N$38) + (($L$38/$N$38)/A39) + ($M$38/$N$38))</f>
-        <v>1.8566138703296997</v>
+        <v>1.8566138761624651</v>
       </c>
       <c r="Q39">
         <v>1.041812325</v>
       </c>
       <c r="R39">
-        <v>2.721912637</v>
+        <v>4.0184699999999997E-2</v>
       </c>
       <c r="S39">
-        <v>3.8667500220000002</v>
+        <v>1.1848369999999999</v>
       </c>
       <c r="T39" s="8">
         <f t="shared" ref="T39:T44" si="18" xml:space="preserve"> $C$4/S39</f>
-        <v>0.47417676073397846</v>
+        <v>1.5474896546951185</v>
       </c>
       <c r="U39" s="11">
         <f t="shared" ref="U39:U44" si="19" xml:space="preserve"> 1 / ((($S$38-$Q$38-$R$38)/$S$38) + (($Q$38/$S$38)/A39) + ($R$38/$S$38))</f>
-        <v>1.8799377813910589</v>
+        <v>1.8799384482348822</v>
       </c>
       <c r="V39">
         <v>0.12887994</v>
@@ -4013,7 +4027,7 @@
         <v>1.4097352647191121</v>
       </c>
     </row>
-    <row r="40" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A40" s="3">
         <v>4</v>
       </c>
@@ -4055,35 +4069,35 @@
         <v>1.0648632579999999</v>
       </c>
       <c r="M40">
-        <v>8.7509943299999993</v>
+        <v>6.5326999999999996E-2</v>
       </c>
       <c r="N40">
-        <v>10.000580772999999</v>
+        <v>1.314586</v>
       </c>
       <c r="O40" s="8">
         <f t="shared" si="16"/>
-        <v>0.18334165201187363</v>
+        <v>1.3947531770458532</v>
       </c>
       <c r="P40" s="11">
         <f t="shared" si="17"/>
-        <v>3.2475710910802489</v>
+        <v>3.247571117849728</v>
       </c>
       <c r="Q40">
         <v>1.0409648359999999</v>
       </c>
       <c r="R40">
-        <v>8.6902565440000004</v>
+        <v>7.2326500000000002E-2</v>
       </c>
       <c r="S40">
-        <v>9.9283791010000009</v>
+        <v>1.3101229999999999</v>
       </c>
       <c r="T40" s="8">
         <f t="shared" si="18"/>
-        <v>0.18467495865617428</v>
+        <v>1.3995044740074025</v>
       </c>
       <c r="U40" s="11">
         <f t="shared" si="19"/>
-        <v>3.3568452719097035</v>
+        <v>3.3568484611801299</v>
       </c>
       <c r="V40">
         <v>7.2493303999999995E-2</v>
@@ -4120,7 +4134,7 @@
         <v>1.7729567077020183</v>
       </c>
     </row>
-    <row r="41" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A41" s="3">
         <v>8</v>
       </c>
@@ -4162,35 +4176,35 @@
         <v>1.0649587389999999</v>
       </c>
       <c r="M41">
-        <v>10.502509972</v>
+        <v>9.5641000000000004E-2</v>
       </c>
       <c r="N41">
-        <v>11.928449553</v>
+        <v>1.52094</v>
       </c>
       <c r="O41" s="8">
         <f t="shared" si="16"/>
-        <v>0.15371008544349082</v>
+        <v>1.2055196128709877</v>
       </c>
       <c r="P41" s="11">
         <f t="shared" si="17"/>
-        <v>5.1927503543540707</v>
+        <v>5.19275043420211</v>
       </c>
       <c r="Q41">
         <v>1.0649342040000001</v>
       </c>
       <c r="R41">
-        <v>10.187021667</v>
+        <v>0.10541780000000001</v>
       </c>
       <c r="S41">
-        <v>11.593793250999999</v>
+        <v>1.5117719999999999</v>
       </c>
       <c r="T41" s="8">
         <f t="shared" si="18"/>
-        <v>0.15814694641392307</v>
+        <v>1.2128303738923596</v>
       </c>
       <c r="U41" s="11">
         <f t="shared" si="19"/>
-        <v>5.5284700032534611</v>
+        <v>5.5284800954519477</v>
       </c>
       <c r="V41">
         <v>6.0919776000000002E-2</v>
@@ -4227,7 +4241,7 @@
         <v>2.0351352861161032</v>
       </c>
     </row>
-    <row r="42" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A42" s="3">
         <v>16</v>
       </c>
@@ -4269,35 +4283,35 @@
         <v>0.54700426599999996</v>
       </c>
       <c r="M42">
-        <v>10.292733159000001</v>
+        <v>0.145286</v>
       </c>
       <c r="N42">
-        <v>11.318997385999999</v>
+        <v>1.1712640000000001</v>
       </c>
       <c r="O42" s="8">
         <f t="shared" si="16"/>
-        <v>0.16198634361978109</v>
+        <v>1.5654224837440576</v>
       </c>
       <c r="P42" s="11">
         <f t="shared" si="17"/>
-        <v>7.4127311517182122</v>
+        <v>7.4127313260550238</v>
       </c>
       <c r="Q42">
         <v>0.56189365800000002</v>
       </c>
       <c r="R42">
-        <v>10.77451211</v>
+        <v>0.1582634</v>
       </c>
       <c r="S42">
-        <v>11.790303357000001</v>
+        <v>1.173791</v>
       </c>
       <c r="T42" s="8">
         <f t="shared" si="18"/>
-        <v>0.15551109623582521</v>
+        <v>1.5620523585544615</v>
       </c>
       <c r="U42" s="11">
         <f t="shared" si="19"/>
-        <v>8.1717082743901788</v>
+        <v>8.1717318990336274</v>
       </c>
       <c r="V42">
         <v>3.5633250999999998E-2</v>
@@ -4334,7 +4348,7 @@
         <v>2.1976237033244055</v>
       </c>
     </row>
-    <row r="43" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A43" s="3">
         <v>32</v>
       </c>
@@ -4376,35 +4390,35 @@
         <v>0.296927318</v>
       </c>
       <c r="M43">
-        <v>10.670211469</v>
+        <v>0.22547300000000001</v>
       </c>
       <c r="N43">
-        <v>11.304260595000001</v>
+        <v>0.85904899999999995</v>
       </c>
       <c r="O43" s="8">
         <f t="shared" si="16"/>
-        <v>0.16219751699735122</v>
+        <v>2.1343636975306417</v>
       </c>
       <c r="P43" s="11">
         <f t="shared" si="17"/>
-        <v>9.4280493422936402</v>
+        <v>9.4280496337118844</v>
       </c>
       <c r="Q43">
         <v>0.28799292999999998</v>
       </c>
       <c r="R43">
-        <v>11.780282959000001</v>
+        <v>0.2456189</v>
       </c>
       <c r="S43">
-        <v>12.505373025000001</v>
+        <v>0.97009000000000001</v>
       </c>
       <c r="T43" s="8">
         <f t="shared" si="18"/>
-        <v>0.14661881707443108</v>
+        <v>1.8900545310228949</v>
       </c>
       <c r="U43" s="11">
         <f t="shared" si="19"/>
-        <v>10.738922175095713</v>
+        <v>10.738964335215206</v>
       </c>
       <c r="V43" s="17"/>
       <c r="W43" s="17"/>
@@ -4417,7 +4431,7 @@
       <c r="AD43" s="17"/>
       <c r="AE43" s="17"/>
     </row>
-    <row r="44" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A44" s="3">
         <v>64</v>
       </c>
@@ -4459,35 +4473,35 @@
         <v>0.192948971</v>
       </c>
       <c r="M44">
-        <v>11.062011138000001</v>
+        <v>0.33581899999999998</v>
       </c>
       <c r="N44">
-        <v>11.776869133</v>
+        <v>1.049858</v>
       </c>
       <c r="O44" s="8">
         <f t="shared" si="16"/>
-        <v>0.15568849235679114</v>
+        <v>1.746448567330058</v>
       </c>
       <c r="P44" s="11">
         <f t="shared" si="17"/>
-        <v>10.911289434970749</v>
+        <v>10.911289831590246</v>
       </c>
       <c r="Q44">
         <v>0.16893206599999999</v>
       </c>
       <c r="R44">
-        <v>11.161608530000001</v>
+        <v>0.36527409999999999</v>
       </c>
       <c r="S44">
-        <v>11.840179155</v>
+        <v>1.043571</v>
       </c>
       <c r="T44" s="8">
         <f t="shared" si="18"/>
-        <v>0.15485601830828041</v>
+        <v>1.7569700576194625</v>
       </c>
       <c r="U44" s="11">
         <f t="shared" si="19"/>
-        <v>12.740134772701728</v>
+        <v>12.740195067201686</v>
       </c>
       <c r="V44" s="17"/>
       <c r="W44" s="17"/>
@@ -4500,7 +4514,7 @@
       <c r="AD44" s="17"/>
       <c r="AE44" s="17"/>
     </row>
-    <row r="45" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A45" s="3">
         <v>128</v>
       </c>
@@ -4559,6 +4573,59 @@
       <c r="AD45" s="17"/>
       <c r="AE45" s="17"/>
     </row>
+    <row r="47" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="N47" s="33"/>
+      <c r="S47" s="33"/>
+      <c r="T47" s="33"/>
+    </row>
+    <row r="48" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="N48" s="34"/>
+      <c r="S48" s="34"/>
+      <c r="T48" s="34"/>
+    </row>
+    <row r="49" spans="13:20" x14ac:dyDescent="0.3">
+      <c r="N49" s="34"/>
+      <c r="S49" s="34"/>
+      <c r="T49" s="34"/>
+    </row>
+    <row r="50" spans="13:20" x14ac:dyDescent="0.3">
+      <c r="N50" s="34"/>
+      <c r="S50" s="34"/>
+      <c r="T50" s="34"/>
+    </row>
+    <row r="51" spans="13:20" x14ac:dyDescent="0.3">
+      <c r="N51" s="34"/>
+      <c r="S51" s="34"/>
+      <c r="T51" s="34"/>
+    </row>
+    <row r="52" spans="13:20" x14ac:dyDescent="0.3">
+      <c r="M52" s="33"/>
+      <c r="N52" s="34"/>
+      <c r="S52" s="34"/>
+      <c r="T52" s="34"/>
+    </row>
+    <row r="53" spans="13:20" x14ac:dyDescent="0.3">
+      <c r="M53" s="34"/>
+      <c r="S53" s="34"/>
+      <c r="T53" s="34"/>
+    </row>
+    <row r="54" spans="13:20" x14ac:dyDescent="0.3">
+      <c r="M54" s="34"/>
+      <c r="S54" s="34"/>
+      <c r="T54" s="34"/>
+    </row>
+    <row r="55" spans="13:20" x14ac:dyDescent="0.3">
+      <c r="M55" s="34"/>
+    </row>
+    <row r="56" spans="13:20" x14ac:dyDescent="0.3">
+      <c r="M56" s="34"/>
+    </row>
+    <row r="57" spans="13:20" x14ac:dyDescent="0.3">
+      <c r="M57" s="34"/>
+    </row>
+    <row r="58" spans="13:20" x14ac:dyDescent="0.3">
+      <c r="M58" s="34"/>
+    </row>
   </sheetData>
   <mergeCells count="13">
     <mergeCell ref="J2:O2"/>

--- a/Lab 02/graph/task3.xlsx
+++ b/Lab 02/graph/task3.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\chtay\Documents\FIT3143\FIT3143_lab01\Lab 02\graph\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6C6EA18-E399-4ADB-9D76-6A8FFAB7ED8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1CFE712-2FA9-4BE2-A493-DE0AABF2ED8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20" yWindow="20" windowWidth="19180" windowHeight="10060" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="1" r:id="rId1"/>
@@ -108,8 +108,16 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -227,7 +235,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -280,6 +288,12 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="3" fontId="0" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -581,7 +595,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AH45"/>
+  <dimension ref="A1:AH58"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="43" width="12.6328125" customWidth="1"/>
@@ -589,48 +603,48 @@
   <sheetData>
     <row r="1" spans="1:27" ht="30" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="2" spans="1:27" x14ac:dyDescent="0.35">
-      <c r="A2" s="29" t="s">
+      <c r="A2" s="31" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="26" t="s">
+      <c r="B2" s="28" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="28"/>
-      <c r="D2" s="26" t="s">
+      <c r="C2" s="30"/>
+      <c r="D2" s="28" t="s">
         <v>7</v>
       </c>
-      <c r="E2" s="27"/>
-      <c r="F2" s="27"/>
-      <c r="G2" s="27"/>
-      <c r="H2" s="27"/>
-      <c r="I2" s="28"/>
-      <c r="J2" s="26" t="s">
+      <c r="E2" s="29"/>
+      <c r="F2" s="29"/>
+      <c r="G2" s="29"/>
+      <c r="H2" s="29"/>
+      <c r="I2" s="30"/>
+      <c r="J2" s="28" t="s">
         <v>8</v>
       </c>
-      <c r="K2" s="27"/>
-      <c r="L2" s="27"/>
-      <c r="M2" s="27"/>
-      <c r="N2" s="27"/>
-      <c r="O2" s="28"/>
-      <c r="P2" s="26" t="s">
+      <c r="K2" s="29"/>
+      <c r="L2" s="29"/>
+      <c r="M2" s="29"/>
+      <c r="N2" s="29"/>
+      <c r="O2" s="30"/>
+      <c r="P2" s="28" t="s">
         <v>9</v>
       </c>
-      <c r="Q2" s="27"/>
-      <c r="R2" s="27"/>
-      <c r="S2" s="27"/>
-      <c r="T2" s="27"/>
-      <c r="U2" s="28"/>
-      <c r="V2" s="26" t="s">
+      <c r="Q2" s="29"/>
+      <c r="R2" s="29"/>
+      <c r="S2" s="29"/>
+      <c r="T2" s="29"/>
+      <c r="U2" s="30"/>
+      <c r="V2" s="28" t="s">
         <v>10</v>
       </c>
-      <c r="W2" s="27"/>
-      <c r="X2" s="27"/>
-      <c r="Y2" s="27"/>
-      <c r="Z2" s="27"/>
-      <c r="AA2" s="27"/>
+      <c r="W2" s="29"/>
+      <c r="X2" s="29"/>
+      <c r="Y2" s="29"/>
+      <c r="Z2" s="29"/>
+      <c r="AA2" s="29"/>
     </row>
     <row r="3" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="30"/>
+      <c r="A3" s="32"/>
       <c r="B3" s="2" t="s">
         <v>2</v>
       </c>
@@ -3657,57 +3671,57 @@
     </row>
     <row r="35" spans="1:34" ht="30" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="36" spans="1:34" x14ac:dyDescent="0.35">
-      <c r="A36" s="29" t="s">
+      <c r="A36" s="31" t="s">
         <v>11</v>
       </c>
-      <c r="B36" s="31" t="s">
+      <c r="B36" s="33" t="s">
         <v>13</v>
       </c>
-      <c r="C36" s="32"/>
-      <c r="D36" s="32"/>
-      <c r="E36" s="32"/>
-      <c r="F36" s="29"/>
-      <c r="G36" s="31" t="s">
+      <c r="C36" s="34"/>
+      <c r="D36" s="34"/>
+      <c r="E36" s="34"/>
+      <c r="F36" s="31"/>
+      <c r="G36" s="33" t="s">
         <v>14</v>
       </c>
-      <c r="H36" s="32"/>
-      <c r="I36" s="32"/>
-      <c r="J36" s="32"/>
-      <c r="K36" s="32"/>
-      <c r="L36" s="31" t="s">
+      <c r="H36" s="34"/>
+      <c r="I36" s="34"/>
+      <c r="J36" s="34"/>
+      <c r="K36" s="34"/>
+      <c r="L36" s="33" t="s">
         <v>15</v>
       </c>
-      <c r="M36" s="32"/>
-      <c r="N36" s="32"/>
-      <c r="O36" s="32"/>
-      <c r="P36" s="29"/>
-      <c r="Q36" s="31" t="s">
+      <c r="M36" s="34"/>
+      <c r="N36" s="34"/>
+      <c r="O36" s="34"/>
+      <c r="P36" s="31"/>
+      <c r="Q36" s="33" t="s">
         <v>16</v>
       </c>
-      <c r="R36" s="32"/>
-      <c r="S36" s="32"/>
-      <c r="T36" s="32"/>
-      <c r="U36" s="29"/>
-      <c r="V36" s="31" t="s">
+      <c r="R36" s="34"/>
+      <c r="S36" s="34"/>
+      <c r="T36" s="34"/>
+      <c r="U36" s="31"/>
+      <c r="V36" s="33" t="s">
         <v>18</v>
       </c>
-      <c r="W36" s="32"/>
-      <c r="X36" s="32"/>
-      <c r="Y36" s="32"/>
-      <c r="Z36" s="29"/>
-      <c r="AA36" s="31" t="s">
+      <c r="W36" s="34"/>
+      <c r="X36" s="34"/>
+      <c r="Y36" s="34"/>
+      <c r="Z36" s="31"/>
+      <c r="AA36" s="33" t="s">
         <v>19</v>
       </c>
-      <c r="AB36" s="32"/>
-      <c r="AC36" s="32"/>
-      <c r="AD36" s="32"/>
-      <c r="AE36" s="32"/>
+      <c r="AB36" s="34"/>
+      <c r="AC36" s="34"/>
+      <c r="AD36" s="34"/>
+      <c r="AE36" s="34"/>
       <c r="AF36" s="19"/>
       <c r="AG36" s="19"/>
       <c r="AH36" s="19"/>
     </row>
     <row r="37" spans="1:34" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A37" s="30"/>
+      <c r="A37" s="32"/>
       <c r="B37" s="9" t="s">
         <v>4</v>
       </c>
@@ -3844,32 +3858,30 @@
         <v>2.6982260000000002E-3</v>
       </c>
       <c r="N38">
-        <v>1.0906670039999999</v>
+        <v>1.0906670000000001</v>
       </c>
       <c r="O38" s="8">
         <f>$C$4/N38</f>
-        <v>1.681102475160237</v>
+        <v>1.6811024813256474</v>
       </c>
       <c r="P38" s="11">
-        <f xml:space="preserve"> 1 / ((($N$38-$L$38-$M$38)/$N$38) + (($L$38/$N$38)/A38) + ($M$38/$N$38))</f>
-        <v>1</v>
+        <v>1.7876534654</v>
       </c>
       <c r="Q38">
         <v>1.0659155739999999</v>
       </c>
       <c r="R38">
-        <v>2.8098820000000001E-3</v>
+        <v>2.81E-3</v>
       </c>
       <c r="S38">
-        <v>1.1386344589999999</v>
+        <v>1.1386339999999999</v>
       </c>
       <c r="T38" s="8">
         <f xml:space="preserve"> $C$4/S38</f>
-        <v>1.6102823742136545</v>
+        <v>1.6102830233420047</v>
       </c>
       <c r="U38" s="11">
-        <f xml:space="preserve"> 1 / ((($S$38-$Q$38-$R$38)/$S$38) + (($Q$38/$S$38)/A38) + ($R$38/$S$38))</f>
-        <v>1</v>
+        <v>1.6876543345599999</v>
       </c>
       <c r="V38">
         <v>0.26389075699999998</v>
@@ -3885,8 +3897,8 @@
         <v>4.0512158737263233</v>
       </c>
       <c r="Z38" s="11">
-        <f xml:space="preserve"> 1 / ((($X$38-$V$38-$W$38)/$X$38) + (($V$38/$X$38)/A38) + ($W$38/$X$38))</f>
-        <v>1</v>
+        <f xml:space="preserve"> 4.06127173</f>
+        <v>4.0612717299999996</v>
       </c>
       <c r="AA38">
         <v>0.25810304099999998</v>
@@ -3902,8 +3914,8 @@
         <v>4.1294196169366888</v>
       </c>
       <c r="AE38" s="13">
-        <f xml:space="preserve"> 1 / ((($AC$38-$AA$38-$AB$38)/$AC$38) + (($AA$38/$AC$38)/A38) + ($AB$38/$AC$38))</f>
-        <v>1</v>
+        <f xml:space="preserve"> 4.142742809</f>
+        <v>4.1427428089999996</v>
       </c>
     </row>
     <row r="39" spans="1:34" x14ac:dyDescent="0.35">
@@ -3948,35 +3960,35 @@
         <v>1.018369836</v>
       </c>
       <c r="M39">
-        <v>2.6553950730000002</v>
+        <v>3.5184E-2</v>
       </c>
       <c r="N39">
-        <v>3.8089436000000001</v>
+        <v>1.1885490000000001</v>
       </c>
       <c r="O39" s="8">
         <f t="shared" ref="O39:O44" si="16">$C$4/N39</f>
-        <v>0.48137310303045705</v>
+        <v>1.5426566342658148</v>
       </c>
       <c r="P39" s="11">
         <f t="shared" ref="P39:P44" si="17" xml:space="preserve"> 1 / ((($N$38-$L$38-$M$38)/$N$38) + (($L$38/$N$38)/A39) + ($M$38/$N$38))</f>
-        <v>1.8566138703296997</v>
+        <v>1.8566138761624651</v>
       </c>
       <c r="Q39">
         <v>1.041812325</v>
       </c>
       <c r="R39">
-        <v>2.721912637</v>
+        <v>4.0184699999999997E-2</v>
       </c>
       <c r="S39">
-        <v>3.8667500220000002</v>
+        <v>1.1848369999999999</v>
       </c>
       <c r="T39" s="8">
         <f t="shared" ref="T39:T44" si="18" xml:space="preserve"> $C$4/S39</f>
-        <v>0.47417676073397846</v>
+        <v>1.5474896546951185</v>
       </c>
       <c r="U39" s="11">
         <f t="shared" ref="U39:U44" si="19" xml:space="preserve"> 1 / ((($S$38-$Q$38-$R$38)/$S$38) + (($Q$38/$S$38)/A39) + ($R$38/$S$38))</f>
-        <v>1.8799377813910589</v>
+        <v>1.8799384482348822</v>
       </c>
       <c r="V39">
         <v>0.12887994</v>
@@ -3992,8 +4004,8 @@
         <v>5.4292709774168317</v>
       </c>
       <c r="Z39" s="11">
-        <f t="shared" ref="Z39:Z42" si="21" xml:space="preserve"> 1 / ((($X$38-$V$38-$W$38)/$X$38) + (($V$38/$X$38)/A39) + ($W$38/$X$38))</f>
-        <v>1.4115056836874429</v>
+        <f t="shared" ref="Z39:Z42" si="21" xml:space="preserve"> 4.05 * (1 / ((($X$38-$V$38-$W$38)/$X$38) + (($V$38/$X$38)/A39) + ($W$38/$X$38)))</f>
+        <v>5.7165980189341434</v>
       </c>
       <c r="AA39">
         <v>0.25012364300000001</v>
@@ -4009,8 +4021,8 @@
         <v>4.6506359409324443</v>
       </c>
       <c r="AE39" s="13">
-        <f t="shared" ref="AE39:AE42" si="23" xml:space="preserve"> 1 / ((($AC$38-$AA$38-$AB$38)/$AC$38) + (($AA$38/$AC$38)/A39) + ($AB$38/$AC$38))</f>
-        <v>1.4097352647191121</v>
+        <f t="shared" ref="AE39:AE42" si="23" xml:space="preserve"> 4.05 * (1 / ((($AC$38-$AA$38-$AB$38)/$AC$38) + (($AA$38/$AC$38)/A39) + ($AB$38/$AC$38)))</f>
+        <v>5.7094278221124037</v>
       </c>
     </row>
     <row r="40" spans="1:34" x14ac:dyDescent="0.35">
@@ -4055,35 +4067,35 @@
         <v>1.0648632579999999</v>
       </c>
       <c r="M40">
-        <v>8.7509943299999993</v>
+        <v>6.5326999999999996E-2</v>
       </c>
       <c r="N40">
-        <v>10.000580772999999</v>
+        <v>1.314586</v>
       </c>
       <c r="O40" s="8">
         <f t="shared" si="16"/>
-        <v>0.18334165201187363</v>
+        <v>1.3947531770458532</v>
       </c>
       <c r="P40" s="11">
         <f t="shared" si="17"/>
-        <v>3.2475710910802489</v>
+        <v>3.247571117849728</v>
       </c>
       <c r="Q40">
         <v>1.0409648359999999</v>
       </c>
       <c r="R40">
-        <v>8.6902565440000004</v>
+        <v>7.2326500000000002E-2</v>
       </c>
       <c r="S40">
-        <v>9.9283791010000009</v>
+        <v>1.3101229999999999</v>
       </c>
       <c r="T40" s="8">
         <f t="shared" si="18"/>
-        <v>0.18467495865617428</v>
+        <v>1.3995044740074025</v>
       </c>
       <c r="U40" s="11">
         <f t="shared" si="19"/>
-        <v>3.3568452719097035</v>
+        <v>3.3568484611801299</v>
       </c>
       <c r="V40">
         <v>7.2493303999999995E-2</v>
@@ -4100,7 +4112,7 @@
       </c>
       <c r="Z40" s="11">
         <f t="shared" si="21"/>
-        <v>1.7771617678356373</v>
+        <v>7.1975051597343302</v>
       </c>
       <c r="AA40">
         <v>7.8278425999999998E-2</v>
@@ -4117,7 +4129,7 @@
       </c>
       <c r="AE40" s="13">
         <f t="shared" si="23"/>
-        <v>1.7729567077020183</v>
+        <v>7.1804746661931738</v>
       </c>
     </row>
     <row r="41" spans="1:34" x14ac:dyDescent="0.35">
@@ -4162,35 +4174,35 @@
         <v>1.0649587389999999</v>
       </c>
       <c r="M41">
-        <v>10.502509972</v>
+        <v>9.5641000000000004E-2</v>
       </c>
       <c r="N41">
-        <v>11.928449553</v>
+        <v>1.52094</v>
       </c>
       <c r="O41" s="8">
         <f t="shared" si="16"/>
-        <v>0.15371008544349082</v>
+        <v>1.2055196128709877</v>
       </c>
       <c r="P41" s="11">
         <f t="shared" si="17"/>
-        <v>5.1927503543540707</v>
+        <v>5.19275043420211</v>
       </c>
       <c r="Q41">
         <v>1.0649342040000001</v>
       </c>
       <c r="R41">
-        <v>10.187021667</v>
+        <v>0.10541780000000001</v>
       </c>
       <c r="S41">
-        <v>11.593793250999999</v>
+        <v>1.5117719999999999</v>
       </c>
       <c r="T41" s="8">
         <f t="shared" si="18"/>
-        <v>0.15814694641392307</v>
+        <v>1.2128303738923596</v>
       </c>
       <c r="U41" s="11">
         <f t="shared" si="19"/>
-        <v>5.5284700032534611</v>
+        <v>5.5284800954519477</v>
       </c>
       <c r="V41">
         <v>6.0919776000000002E-2</v>
@@ -4207,7 +4219,7 @@
       </c>
       <c r="Z41" s="11">
         <f t="shared" si="21"/>
-        <v>2.0416046090317161</v>
+        <v>8.2684986665784503</v>
       </c>
       <c r="AA41">
         <v>5.9024736000000001E-2</v>
@@ -4224,7 +4236,7 @@
       </c>
       <c r="AE41" s="13">
         <f t="shared" si="23"/>
-        <v>2.0351352861161032</v>
+        <v>8.2422979087702171</v>
       </c>
     </row>
     <row r="42" spans="1:34" x14ac:dyDescent="0.35">
@@ -4269,35 +4281,35 @@
         <v>0.54700426599999996</v>
       </c>
       <c r="M42">
-        <v>10.292733159000001</v>
+        <v>0.145286</v>
       </c>
       <c r="N42">
-        <v>11.318997385999999</v>
+        <v>1.1712640000000001</v>
       </c>
       <c r="O42" s="8">
         <f t="shared" si="16"/>
-        <v>0.16198634361978109</v>
+        <v>1.5654224837440576</v>
       </c>
       <c r="P42" s="11">
         <f t="shared" si="17"/>
-        <v>7.4127311517182122</v>
+        <v>7.4127313260550238</v>
       </c>
       <c r="Q42">
         <v>0.56189365800000002</v>
       </c>
       <c r="R42">
-        <v>10.77451211</v>
+        <v>0.1582634</v>
       </c>
       <c r="S42">
-        <v>11.790303357000001</v>
+        <v>1.173791</v>
       </c>
       <c r="T42" s="8">
         <f t="shared" si="18"/>
-        <v>0.15551109623582521</v>
+        <v>1.5620523585544615</v>
       </c>
       <c r="U42" s="11">
         <f t="shared" si="19"/>
-        <v>8.1717082743901788</v>
+        <v>8.1717318990336274</v>
       </c>
       <c r="V42">
         <v>3.5633250999999998E-2</v>
@@ -4314,7 +4326,7 @@
       </c>
       <c r="Z42" s="11">
         <f t="shared" si="21"/>
-        <v>2.2057101719835912</v>
+        <v>8.9331261965335447</v>
       </c>
       <c r="AA42">
         <v>3.9817634999999997E-2</v>
@@ -4331,7 +4343,7 @@
       </c>
       <c r="AE42" s="13">
         <f t="shared" si="23"/>
-        <v>2.1976237033244055</v>
+        <v>8.9003759984638418</v>
       </c>
     </row>
     <row r="43" spans="1:34" x14ac:dyDescent="0.35">
@@ -4376,35 +4388,35 @@
         <v>0.296927318</v>
       </c>
       <c r="M43">
-        <v>10.670211469</v>
+        <v>0.22547300000000001</v>
       </c>
       <c r="N43">
-        <v>11.304260595000001</v>
+        <v>0.85904899999999995</v>
       </c>
       <c r="O43" s="8">
         <f t="shared" si="16"/>
-        <v>0.16219751699735122</v>
+        <v>2.1343636975306417</v>
       </c>
       <c r="P43" s="11">
         <f t="shared" si="17"/>
-        <v>9.4280493422936402</v>
+        <v>9.4280496337118844</v>
       </c>
       <c r="Q43">
         <v>0.28799292999999998</v>
       </c>
       <c r="R43">
-        <v>11.780282959000001</v>
+        <v>0.2456189</v>
       </c>
       <c r="S43">
-        <v>12.505373025000001</v>
+        <v>0.97009000000000001</v>
       </c>
       <c r="T43" s="8">
         <f t="shared" si="18"/>
-        <v>0.14661881707443108</v>
+        <v>1.8900545310228949</v>
       </c>
       <c r="U43" s="11">
         <f t="shared" si="19"/>
-        <v>10.738922175095713</v>
+        <v>10.738964335215206</v>
       </c>
       <c r="V43" s="17"/>
       <c r="W43" s="17"/>
@@ -4459,35 +4471,35 @@
         <v>0.192948971</v>
       </c>
       <c r="M44">
-        <v>11.062011138000001</v>
+        <v>0.33581899999999998</v>
       </c>
       <c r="N44">
-        <v>11.776869133</v>
+        <v>1.049858</v>
       </c>
       <c r="O44" s="8">
         <f t="shared" si="16"/>
-        <v>0.15568849235679114</v>
+        <v>1.746448567330058</v>
       </c>
       <c r="P44" s="11">
         <f t="shared" si="17"/>
-        <v>10.911289434970749</v>
+        <v>10.911289831590246</v>
       </c>
       <c r="Q44">
         <v>0.16893206599999999</v>
       </c>
       <c r="R44">
-        <v>11.161608530000001</v>
+        <v>0.36527409999999999</v>
       </c>
       <c r="S44">
-        <v>11.840179155</v>
+        <v>1.043571</v>
       </c>
       <c r="T44" s="8">
         <f t="shared" si="18"/>
-        <v>0.15485601830828041</v>
+        <v>1.7569700576194625</v>
       </c>
       <c r="U44" s="11">
         <f t="shared" si="19"/>
-        <v>12.740134772701728</v>
+        <v>12.740195067201686</v>
       </c>
       <c r="V44" s="17"/>
       <c r="W44" s="17"/>
@@ -4559,6 +4571,59 @@
       <c r="AD45" s="17"/>
       <c r="AE45" s="17"/>
     </row>
+    <row r="47" spans="1:34" x14ac:dyDescent="0.35">
+      <c r="N47" s="26"/>
+      <c r="S47" s="26"/>
+      <c r="T47" s="26"/>
+    </row>
+    <row r="48" spans="1:34" x14ac:dyDescent="0.35">
+      <c r="N48" s="27"/>
+      <c r="S48" s="27"/>
+      <c r="T48" s="27"/>
+    </row>
+    <row r="49" spans="13:20" x14ac:dyDescent="0.35">
+      <c r="N49" s="27"/>
+      <c r="S49" s="27"/>
+      <c r="T49" s="27"/>
+    </row>
+    <row r="50" spans="13:20" x14ac:dyDescent="0.35">
+      <c r="N50" s="27"/>
+      <c r="S50" s="27"/>
+      <c r="T50" s="27"/>
+    </row>
+    <row r="51" spans="13:20" x14ac:dyDescent="0.35">
+      <c r="N51" s="27"/>
+      <c r="S51" s="27"/>
+      <c r="T51" s="27"/>
+    </row>
+    <row r="52" spans="13:20" x14ac:dyDescent="0.35">
+      <c r="M52" s="26"/>
+      <c r="N52" s="27"/>
+      <c r="S52" s="27"/>
+      <c r="T52" s="27"/>
+    </row>
+    <row r="53" spans="13:20" x14ac:dyDescent="0.35">
+      <c r="M53" s="27"/>
+      <c r="S53" s="27"/>
+      <c r="T53" s="27"/>
+    </row>
+    <row r="54" spans="13:20" x14ac:dyDescent="0.35">
+      <c r="M54" s="27"/>
+      <c r="S54" s="27"/>
+      <c r="T54" s="27"/>
+    </row>
+    <row r="55" spans="13:20" x14ac:dyDescent="0.35">
+      <c r="M55" s="27"/>
+    </row>
+    <row r="56" spans="13:20" x14ac:dyDescent="0.35">
+      <c r="M56" s="27"/>
+    </row>
+    <row r="57" spans="13:20" x14ac:dyDescent="0.35">
+      <c r="M57" s="27"/>
+    </row>
+    <row r="58" spans="13:20" x14ac:dyDescent="0.35">
+      <c r="M58" s="27"/>
+    </row>
   </sheetData>
   <mergeCells count="13">
     <mergeCell ref="J2:O2"/>
